--- a/rapporten/prijsrapport-BE-2026-05-06.xlsx
+++ b/rapporten/prijsrapport-BE-2026-05-06.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="513">
   <si>
     <t>Product</t>
   </si>
@@ -37,69 +37,123 @@
     <t>Fulfilment</t>
   </si>
   <si>
+    <t>Omerta - Signature Pack - set van 3x100ml</t>
+  </si>
+  <si>
     <t>8720938379314</t>
   </si>
   <si>
-    <t>1247304</t>
+    <t>Meeuwenberg Im- en Export</t>
   </si>
   <si>
     <t>FBR</t>
   </si>
   <si>
+    <t>Omerta - Night Power Pack - set van 3x100ml</t>
+  </si>
+  <si>
     <t>8720938379284</t>
   </si>
   <si>
+    <t>Omerta - Seduction Pack - set van 3x100ml</t>
+  </si>
+  <si>
     <t>8720938379260</t>
   </si>
   <si>
+    <t>Omerta - Wild energy Pack - set van 3x100ml</t>
+  </si>
+  <si>
     <t>8720938379291</t>
   </si>
   <si>
+    <t>Omerta - Daily Elegance Pack - set van 3x100ml</t>
+  </si>
+  <si>
     <t>8720938379222</t>
   </si>
   <si>
+    <t>Omerta - Night Out Pack - set van 3x100ml</t>
+  </si>
+  <si>
     <t>8720938379239</t>
   </si>
   <si>
     <t>8720938379307</t>
   </si>
   <si>
+    <t>Creation Lamis Overdrive Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>6291012000261</t>
   </si>
   <si>
+    <t>Azira - Royal Oud - Eau de Parfum Unisex</t>
+  </si>
+  <si>
     <t>8721349102720</t>
   </si>
   <si>
+    <t>Azira - Dream Oasis - Eau de Parfum Unisex</t>
+  </si>
+  <si>
     <t>8721349102706</t>
   </si>
   <si>
+    <t>Bubble Bliss - Like a Fairytale - Dreamy Daisy - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+  </si>
+  <si>
     <t>8721055494232</t>
   </si>
   <si>
-    <t>946246</t>
+    <t>Minimarkt W&amp;M</t>
+  </si>
+  <si>
+    <t>Hello Kitty-Strawberry-15ml Eau de Parfum</t>
   </si>
   <si>
     <t>7640158816639</t>
   </si>
   <si>
+    <t>Hello Kitty-Cotton Candy- suikerspin - 15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816691</t>
   </si>
   <si>
+    <t>Bubble Bliss - Like a Fairytale - Glimmering Grace - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+  </si>
+  <si>
     <t>8721055494263</t>
   </si>
   <si>
+    <t>Hello Kitty-Peach-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816677</t>
   </si>
   <si>
+    <t>Hello Kitty-Apple-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816714</t>
   </si>
   <si>
+    <t>Hello Kitty-Spring Time-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816837</t>
   </si>
   <si>
+    <t>Hello Kitty-Coconut-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816615</t>
   </si>
   <si>
+    <t>Bubble Bliss - Like a Fairytale - Lovely Lily - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+  </si>
+  <si>
     <t>8721055494225</t>
   </si>
   <si>
@@ -121,19 +175,31 @@
     <t>8721055493198</t>
   </si>
   <si>
+    <t>Hello Kitty-Rainbow-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>8721055493211</t>
   </si>
   <si>
+    <t>Omerta - La Donna X - Eau De Parfum - for women - 100ML</t>
+  </si>
+  <si>
     <t>8715658380580</t>
   </si>
   <si>
-    <t>1840300</t>
+    <t>Bliksma Retail B.V.</t>
+  </si>
+  <si>
+    <t>Omerta - Golden Challenge Ladies World - Eau De Parfum - 100ML</t>
   </si>
   <si>
     <t>8715658997993</t>
   </si>
   <si>
-    <t>1762224</t>
+    <t>Koopjesfun.nl</t>
+  </si>
+  <si>
+    <t>Omerta - Express Sensualite Energy - Eau De Parfum - 100ML</t>
   </si>
   <si>
     <t>8715658998839</t>
@@ -178,24 +244,39 @@
     <t>8715658999249</t>
   </si>
   <si>
+    <t>NG Dark Elixir Men Eau de Toilette 100 ml</t>
+  </si>
+  <si>
     <t>8719214757229</t>
   </si>
   <si>
-    <t>1848839</t>
+    <t>Parfum-Land-graaf.nl</t>
   </si>
   <si>
     <t>8715658370017</t>
   </si>
   <si>
+    <t>NG Home Perfume - Bella Vida - Set van 3st</t>
+  </si>
+  <si>
     <t>6151028518580</t>
   </si>
   <si>
+    <t>NG Home Perfume - Next Fragrance - Set van 3st</t>
+  </si>
+  <si>
     <t>6151028322347</t>
   </si>
   <si>
+    <t>NG Home Perfume - Crystal Pink - Set van 3st</t>
+  </si>
+  <si>
     <t>6151029165127</t>
   </si>
   <si>
+    <t>NG Home Perfume - Predator - Set van 3st</t>
+  </si>
+  <si>
     <t>6151028763713</t>
   </si>
   <si>
@@ -205,7 +286,7 @@
     <t>8715658350125</t>
   </si>
   <si>
-    <t>1811531</t>
+    <t>JD-specials</t>
   </si>
   <si>
     <t>8719214751661</t>
@@ -214,13 +295,16 @@
     <t>1738467</t>
   </si>
   <si>
+    <t>Omerta - Love Dust - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658380115</t>
   </si>
   <si>
     <t>8715658370062</t>
   </si>
   <si>
-    <t>1757721</t>
+    <t>ParfumDeo.nl</t>
   </si>
   <si>
     <t>8715658999638</t>
@@ -229,6 +313,9 @@
     <t>8719214750053</t>
   </si>
   <si>
+    <t>Linn - Young Oui Je T'Aime Mon Amour - Eau De Parfum - 100Ml</t>
+  </si>
+  <si>
     <t>8715658400417</t>
   </si>
   <si>
@@ -244,15 +331,27 @@
     <t>8721055492795</t>
   </si>
   <si>
+    <t>NG -Next Fragranse For Her- 100ml Eau de Parfum-50ml Showergel-50ml Bodylotion</t>
+  </si>
+  <si>
     <t>8719214755829</t>
   </si>
   <si>
+    <t>Omerta -X Emotion- Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8715658380689</t>
   </si>
   <si>
+    <t>Dorall Win Over parfum - Eau de Toilette voor haar - 100ml</t>
+  </si>
+  <si>
     <t>6291012874428</t>
   </si>
   <si>
+    <t>Real Time - Smart Guy For Men - Eau de toilette - 100ML</t>
+  </si>
+  <si>
     <t>8715658350507</t>
   </si>
   <si>
@@ -268,21 +367,39 @@
     <t>8719214753344</t>
   </si>
   <si>
+    <t>NG Home Bella Vida Geurstokjes 200ml</t>
+  </si>
+  <si>
     <t>8719214754549</t>
   </si>
   <si>
+    <t>MEEKA Ouvert Eau de Parfum - Bloemige geur met lavendel en oranjebloesem - 100ml</t>
+  </si>
+  <si>
     <t>8719214754105</t>
   </si>
   <si>
+    <t>NG Home Predator Geurstokjes 200ml</t>
+  </si>
+  <si>
     <t>6151027816809</t>
   </si>
   <si>
+    <t>Real Time - Fine Gold Pink Vibrations - Eau de parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658361015</t>
   </si>
   <si>
+    <t>Real Time - Journee Joyeuse - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658360018</t>
   </si>
   <si>
+    <t>Real Time Coup d'Amour eau de parfum 100 ml.</t>
+  </si>
+  <si>
     <t>8715658360063</t>
   </si>
   <si>
@@ -298,10 +415,16 @@
     <t>8719214750084</t>
   </si>
   <si>
+    <t>Dorall -Le Homme Noir- Eau de Toilette 100ml</t>
+  </si>
+  <si>
     <t>6291012905726</t>
   </si>
   <si>
-    <t>1580482</t>
+    <t>PTM Trading</t>
+  </si>
+  <si>
+    <t>Real Time King Sky Eau de Toilette 100ml</t>
   </si>
   <si>
     <t>8715658002932</t>
@@ -310,90 +433,168 @@
     <t>8715658002789</t>
   </si>
   <si>
+    <t>Sentio Love &amp; Casual for Him Eau de Toilette Spray 100 ml</t>
+  </si>
+  <si>
     <t>8721055493723</t>
   </si>
   <si>
+    <t>Sentio - mini parfum - Best Friend Ever - heren - vaderdag - eau de toilette - 15 ml</t>
+  </si>
+  <si>
     <t>8721055490524</t>
   </si>
   <si>
-    <t>1724898</t>
+    <t>jb ballonnen and more</t>
   </si>
   <si>
     <t>7640158817810</t>
   </si>
   <si>
-    <t>1715463</t>
+    <t>TM BOOKS</t>
+  </si>
+  <si>
+    <t>NG - Burnt Vanilla - Eau de Parfum 100ml</t>
   </si>
   <si>
     <t>8719214750237</t>
   </si>
   <si>
+    <t>NG Mrs. Unique parfum - Eau de parfum voor dames - 100ml</t>
+  </si>
+  <si>
     <t>8719214758349</t>
   </si>
   <si>
+    <t>TBY - To Be Talented - 100ml Eau de Toilette voor mannen</t>
+  </si>
+  <si>
     <t>8719214756529</t>
   </si>
   <si>
+    <t>NG Femme Brilliant Eau de Parfum 100 ml - Next Generation</t>
+  </si>
+  <si>
     <t>8719214755003</t>
   </si>
   <si>
+    <t>NG - SERENE PATH - 100ml Eau de Parfum for Women</t>
+  </si>
+  <si>
     <t>8719214756895</t>
   </si>
   <si>
+    <t>NG Routines de L'Homme Eau de Toilette 100ml</t>
+  </si>
+  <si>
     <t>8719214758332</t>
   </si>
   <si>
+    <t>TBY - To Be Uniquer - 100ml Eau de Parfum voor vrouwen</t>
+  </si>
+  <si>
     <t>8719214756574</t>
   </si>
   <si>
+    <t>NG Perfumes Golddigger Woman eau de parfum 90 ml</t>
+  </si>
+  <si>
     <t>8719214753009</t>
   </si>
   <si>
+    <t>TBY - To Be Edgy - 100ml Eau de Parfum voor vrouwen</t>
+  </si>
+  <si>
     <t>8719214756536</t>
   </si>
   <si>
+    <t>NG Predator for Women 100ml + 15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>6013909650621</t>
   </si>
   <si>
+    <t>TBY - To Be Passionate - 100ml Eau de Parfum voor vrouwen</t>
+  </si>
+  <si>
     <t>8719214756543</t>
   </si>
   <si>
+    <t>TBY - To Be Awesome - 100ml Eau de Toilette voor vmannen</t>
+  </si>
+  <si>
     <t>8719214756482</t>
   </si>
   <si>
+    <t>NG - SHE IS HERE - 100ml Eau de Parfum for Women</t>
+  </si>
+  <si>
     <t>8719214757052</t>
   </si>
   <si>
+    <t>NG - HE IS HERE - 100ml Eau de Toilette for Men</t>
+  </si>
+  <si>
     <t>8719214757038</t>
   </si>
   <si>
+    <t>TBY - To Be Successful - 100ml Eau de Toilette voor mannen</t>
+  </si>
+  <si>
     <t>8719214756512</t>
   </si>
   <si>
+    <t>TBY - To Be Strong - 100ml Eau de Toilette voor mannen</t>
+  </si>
+  <si>
     <t>8719214756505</t>
   </si>
   <si>
+    <t>TBY - To Be Pleased - 100ml Eau de Parfum voor vrouwen</t>
+  </si>
+  <si>
     <t>8719214756550</t>
   </si>
   <si>
+    <t>NG Dominatio Woman Eau de Parfum - Damesparfum met frisse en elegante geur - 100ml</t>
+  </si>
+  <si>
     <t>7438235478494</t>
   </si>
   <si>
+    <t>NG Elinne Eau de Parfum - 90ml</t>
+  </si>
+  <si>
     <t>8719214758356</t>
   </si>
   <si>
+    <t>TBY - To Be Sparkling - 100ml Eau de Parfum voor vrouwen</t>
+  </si>
+  <si>
     <t>8719214756567</t>
   </si>
   <si>
+    <t>TBY - To Be Young - 100ml Eau de Parfum voor vrouwen</t>
+  </si>
+  <si>
     <t>8719214756581</t>
   </si>
   <si>
+    <t>Next Generation Next Fragrance Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8719214753313</t>
   </si>
   <si>
+    <t>NG Heavens Body 100ML Dames Eau de Parfum</t>
+  </si>
+  <si>
     <t>8719214751920</t>
   </si>
   <si>
+    <t>NG Lightness Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8719214758363</t>
   </si>
   <si>
@@ -448,6 +649,9 @@
     <t>8719214753641</t>
   </si>
   <si>
+    <t>Omerta Oh My Dear L'extase parfum - Eau de parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658380245</t>
   </si>
   <si>
@@ -457,10 +661,13 @@
     <t>8715658350521</t>
   </si>
   <si>
+    <t>8715658360759</t>
+  </si>
+  <si>
     <t>8718421831197</t>
   </si>
   <si>
-    <t>8715658360759</t>
+    <t>Sentio - mini parfum - Lucky Numbers 4 Four Ever - eau de parfum - 15ml</t>
   </si>
   <si>
     <t>8721055490364</t>
@@ -469,46 +676,85 @@
     <t>6291012884939</t>
   </si>
   <si>
+    <t>Real Time - Miss Sexy - Pour Femme Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8715658007036</t>
   </si>
   <si>
+    <t>NG -Crystal Pink Giftset- 100ml Eau de Parfum 50ml Showergel 50ml Bodylotion</t>
+  </si>
+  <si>
     <t>8719214755805</t>
   </si>
   <si>
+    <t>Sentio Ex Plode Fusion eau de parfum Miniparfum for women 15 ml</t>
+  </si>
+  <si>
     <t>7640158816042</t>
   </si>
   <si>
-    <t>1808661</t>
+    <t>Singh repair service v.o.f</t>
+  </si>
+  <si>
+    <t>NG Femme L'odeur du NG Giftset</t>
   </si>
   <si>
     <t>8719214753290</t>
   </si>
   <si>
+    <t>Omerta - Royal X - Eau de toilette - 100ML</t>
+  </si>
+  <si>
     <t>8715658370260</t>
   </si>
   <si>
+    <t>NG Predator Giftset</t>
+  </si>
+  <si>
     <t>8719214753283</t>
   </si>
   <si>
+    <t>Sentio - mini parfum - I love You - heren - vaderdag - eau de toilette - 15 ml</t>
+  </si>
+  <si>
     <t>8721055490517</t>
   </si>
   <si>
+    <t>Real TimeFijn Goud 999.9 Voor Mannen Eau de Toilette Spray 100ml</t>
+  </si>
+  <si>
     <t>8715658350262</t>
   </si>
   <si>
+    <t>NG Darkness for Men Giftset</t>
+  </si>
+  <si>
     <t>8719214758530</t>
   </si>
   <si>
+    <t>Sentio Paradise Miniparfum Hawaï Waves eau de parfum for women 15 ml</t>
+  </si>
+  <si>
     <t>7640158818855</t>
   </si>
   <si>
+    <t>Sentio Paradise Miniparfum Rio Rhythm eau de parfum for women 15 ml</t>
+  </si>
+  <si>
     <t>7640158818862</t>
   </si>
   <si>
+    <t>Paris Memories - Nagellak - goudbruin - nummer 274 - 1 flesje met 11 ml.</t>
+  </si>
+  <si>
     <t>5414665008786</t>
   </si>
   <si>
-    <t>1330795</t>
+    <t>Totallybeauty</t>
+  </si>
+  <si>
+    <t>Paris Memories - Nagellak - oranje - nummer 301 - 1 flesje met 11 ml.</t>
   </si>
   <si>
     <t>5414665011861</t>
@@ -523,46 +769,79 @@
     <t>1539744</t>
   </si>
   <si>
+    <t>Real Time - Racing Horse Gold - Eau de toilette - 100ML</t>
+  </si>
+  <si>
     <t>8715658350255</t>
   </si>
   <si>
+    <t>NG Lightness for Women miniparfum eau de parfum 15ml</t>
+  </si>
+  <si>
     <t>8719214759162</t>
   </si>
   <si>
+    <t>Georges Mezotti - Queen of Temptation Passion - Eau de parfum 100ml</t>
+  </si>
+  <si>
     <t>8715658420132</t>
   </si>
   <si>
-    <t>1816883</t>
+    <t>DeDaRo Handel</t>
+  </si>
+  <si>
+    <t>Omerta - Sweet Pommy - Eau de parfum - 100ML</t>
   </si>
   <si>
     <t>8715658998563</t>
   </si>
   <si>
-    <t>1503122</t>
+    <t>Beauty by Filou</t>
+  </si>
+  <si>
+    <t>Georges Mezotti - Queen of Temptation Seduction - Eau de parfum 100ml</t>
   </si>
   <si>
     <t>8715658420156</t>
   </si>
   <si>
+    <t>Creation Lamis - Espy - Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>5414666016452</t>
   </si>
   <si>
+    <t>Hello Kitty - Giftset - Delicate Flower - Showergel + Eau de Parfum - Cadeauset voor Kinderen - Geschenkset</t>
+  </si>
+  <si>
     <t>7640158816950</t>
   </si>
   <si>
+    <t>Bubble Bliss Parfum Giftbag Glimmering Grace EDP voor meisjes 50ml</t>
+  </si>
+  <si>
     <t>8721055494324</t>
   </si>
   <si>
+    <t>Linn Young "Je Suis Sure Et Certaine" Eau de parfum 100ml</t>
+  </si>
+  <si>
     <t>8715658400295</t>
   </si>
   <si>
     <t>8719214759193</t>
   </si>
   <si>
+    <t>Sentio Best Friend Ever eau de parfum voor vrouwen - 15ml</t>
+  </si>
+  <si>
     <t>7640158816141</t>
   </si>
   <si>
-    <t>1550659</t>
+    <t>VerpakkingDeals.nl</t>
+  </si>
+  <si>
+    <t>Omerta Power Boost For Men Eau de Toilette Spray 100ml</t>
   </si>
   <si>
     <t>8715658370208</t>
@@ -574,16 +853,22 @@
     <t>8715658008354</t>
   </si>
   <si>
+    <t>Sentio Suffix woman edp 15ml</t>
+  </si>
+  <si>
     <t>0764158815106</t>
   </si>
   <si>
-    <t>1811367</t>
+    <t>Party&amp;more</t>
+  </si>
+  <si>
+    <t>Sentio Miniparfum Cocktail - ESPRESSO MARTINI - Eau de parfum For Her 15ml</t>
   </si>
   <si>
     <t>7640158818787</t>
   </si>
   <si>
-    <t>1835778</t>
+    <t>Dalphin Store</t>
   </si>
   <si>
     <t>8721055490500</t>
@@ -592,54 +877,105 @@
     <t>8721055490340</t>
   </si>
   <si>
+    <t>NG Spectre Fragrances INHUMANE for her eau de parfum 100ml</t>
+  </si>
+  <si>
     <t>8719214757403</t>
   </si>
   <si>
+    <t>NG Spectre Fragrances Your Luxe for her eau de parfum 100ml</t>
+  </si>
+  <si>
     <t>8719214757458</t>
   </si>
   <si>
+    <t>NG Spectre Fragrances GOLD GENERATION for her eau de parfum 100ml</t>
+  </si>
+  <si>
     <t>8719214757397</t>
   </si>
   <si>
+    <t>NG Spectre Fragrances Excelsus MEN For Men eau de toilette 100ml</t>
+  </si>
+  <si>
     <t>8719214757502</t>
   </si>
   <si>
+    <t>NG Spectre Fragrances ALTHEA for her eau de parfum 100ml</t>
+  </si>
+  <si>
     <t>8719214757342</t>
   </si>
   <si>
+    <t>NG Spectre Fragrances Cerulean Blue for her eau de parfum 100ml</t>
+  </si>
+  <si>
     <t>8719214757359</t>
   </si>
   <si>
+    <t>NG Spectre Fragrances Cheff For Men eau de toilette 100ml</t>
+  </si>
+  <si>
     <t>8719214757496</t>
   </si>
   <si>
+    <t>NG Spectre Fragrances Bruyant For Men eau de toilette 100ml</t>
+  </si>
+  <si>
     <t>8719214757489</t>
   </si>
   <si>
+    <t>NG Spectre Fragrances NARIGUEZ for her eau de parfum 100ml</t>
+  </si>
+  <si>
     <t>8719214757427</t>
   </si>
   <si>
+    <t>Hello Kitty You're Cute Eau de Parfum voor Kinderen 50ml</t>
+  </si>
+  <si>
     <t>8721055493303</t>
   </si>
   <si>
+    <t>NG Spectre Fragrances Noré for her eau de parfum 100ml</t>
+  </si>
+  <si>
     <t>8719214757434</t>
   </si>
   <si>
+    <t>Sentio Parfum Life Like Bella Eau de Parfum for her 35ml</t>
+  </si>
+  <si>
     <t>7640158815793</t>
   </si>
   <si>
+    <t>NG Spectre Fragrances Floret for her eau de parfum 100ml</t>
+  </si>
+  <si>
     <t>8719214757380</t>
   </si>
   <si>
+    <t>NG Spectre Fragrances Floralle for her eau de parfum 100ml</t>
+  </si>
+  <si>
     <t>8719214757373</t>
   </si>
   <si>
+    <t>NG Spectre Fragrances UNTOUCHABLE for her eau de parfum 100ml</t>
+  </si>
+  <si>
     <t>8719214757410</t>
   </si>
   <si>
+    <t>NG Spectre Fragrances Blue Onyx For Men eau de toilette 100ml</t>
+  </si>
+  <si>
     <t>8719214757465</t>
   </si>
   <si>
+    <t>NG Spectre Fragrances Alvino EL HOMBRE For Men eau de toilette 100ml</t>
+  </si>
+  <si>
     <t>8719214757472</t>
   </si>
   <si>
@@ -661,42 +997,75 @@
     <t>8715658360056</t>
   </si>
   <si>
+    <t>Atelier Privee Mistical France Unisex - Dark Valor - Eau de Parfum - 100ml</t>
+  </si>
+  <si>
     <t>8721055495802</t>
   </si>
   <si>
-    <t>1421748</t>
+    <t>DrogisterijPlus.nl</t>
   </si>
   <si>
     <t>8719214754563</t>
   </si>
   <si>
+    <t>NG Caught Men Eau de Toilette Spray 100 ml</t>
+  </si>
+  <si>
     <t>8719214750954</t>
   </si>
   <si>
+    <t>Real Time - Kindlooks For Women - Eau de parfum - 100</t>
+  </si>
+  <si>
     <t>8715658002574</t>
   </si>
   <si>
+    <t>NG Spectre Fragrances Gold Generation MEN For Men eau de toilette 100ml</t>
+  </si>
+  <si>
     <t>8719214757519</t>
   </si>
   <si>
+    <t>Omerta - Wild Poppy - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658380023</t>
   </si>
   <si>
+    <t>Creation Lamis - Arrivederci - 100 ml - Eau de Toilette - Herenparfum</t>
+  </si>
+  <si>
     <t>6013905032025</t>
   </si>
   <si>
+    <t>Creation Lamis Paraverse 100ml Eau de Parfum for women</t>
+  </si>
+  <si>
     <t>6291012005082</t>
   </si>
   <si>
+    <t>Bubble Bliss - Giftset - You're Flamazing - Showergel + Eau de Parfum - Cadeauset voor Kinderen - Geschenkset</t>
+  </si>
+  <si>
     <t>8721055494003</t>
   </si>
   <si>
+    <t>Creation Lamis - Golden Wave for him - Eau de Toilette 100ml</t>
+  </si>
+  <si>
     <t>5414666009485</t>
   </si>
   <si>
+    <t>Creation Lamis My Spirit Eau de Parfum For Women 100ml</t>
+  </si>
+  <si>
     <t>6291012005648</t>
   </si>
   <si>
+    <t>NG-DOMINATIO-Eau de Toilette For Men 15ml</t>
+  </si>
+  <si>
     <t>8719214750787</t>
   </si>
   <si>
@@ -706,19 +1075,31 @@
     <t>8721055493068</t>
   </si>
   <si>
+    <t>Linn Young - Outerspace Women - Eau de parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658401308</t>
   </si>
   <si>
+    <t>Linn Young - Outerspace Reborn Women - Eau de parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658401292</t>
   </si>
   <si>
+    <t>Creation Lamis Diva Essence Eau de Parfum For Women 100ml</t>
+  </si>
+  <si>
     <t>6291012005662</t>
   </si>
   <si>
+    <t>Linn Young - Dangerzone - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658998631</t>
   </si>
   <si>
-    <t>1020534</t>
+    <t xml:space="preserve">Parfum Styling Company Europe </t>
   </si>
   <si>
     <t>8719214750657</t>
@@ -730,18 +1111,33 @@
     <t>1831682</t>
   </si>
   <si>
+    <t>Sentio Rojo 045 Giftset - Unisex Eau de Parfum (100ml) &amp; Showergel - Luxe Houtachtige Geur</t>
+  </si>
+  <si>
     <t>7640158818107</t>
   </si>
   <si>
+    <t>Hello Kitty - Giftset - Sweet Leopard Pink - Eau de Parfum + Bodymist - Cadeauset voor Kinderen - Geschenkset</t>
+  </si>
+  <si>
     <t>8721055496373</t>
   </si>
   <si>
+    <t>Real Time - Queen Of Space Glorious - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658361473</t>
   </si>
   <si>
+    <t>Atelier Privee Mistical France parfum - Unisex eau de parfum met rozengeur - 100ml</t>
+  </si>
+  <si>
     <t>8721055495741</t>
   </si>
   <si>
+    <t>Sentio Ex Plode Crush eau de parfum Miniparfum for women 15 ml</t>
+  </si>
+  <si>
     <t>7640158816059</t>
   </si>
   <si>
@@ -751,75 +1147,147 @@
     <t>6291012905399</t>
   </si>
   <si>
+    <t>Real Time - Yes Call Me - Eau de parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658360964</t>
   </si>
   <si>
+    <t>Omerta - Fair Fight - Eau De Toilette - 100Ml</t>
+  </si>
+  <si>
     <t>8715658997924</t>
   </si>
   <si>
+    <t>Omerta Omd Oh My Dear 100 ml - Eau De Parfum Spray Damesparfum</t>
+  </si>
+  <si>
     <t>8715658380030</t>
   </si>
   <si>
+    <t>Omerta -Meet Me Extreme- 100ml Eau de Toilette for men</t>
+  </si>
+  <si>
     <t>8715658370420</t>
   </si>
   <si>
+    <t>Sentio Inter Feer men Eau de toilette spray for him 100ml</t>
+  </si>
+  <si>
     <t>7640158815021</t>
   </si>
   <si>
+    <t>Real Time Canyon night 100 ml eau de toilette spray</t>
+  </si>
+  <si>
     <t>8715658002796</t>
   </si>
   <si>
+    <t>Real Time - Sea Beach - Eau De Toilette - 100ML</t>
+  </si>
+  <si>
     <t>8715658002840</t>
   </si>
   <si>
+    <t>Omerta - Conclude Oud Orient Perfection - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658370550</t>
   </si>
   <si>
+    <t>Vibezz Blissful Life parfum - Eau de parfum voor haar - 100ml</t>
+  </si>
+  <si>
     <t>7640158819180</t>
   </si>
   <si>
+    <t>Real Time Wild Action Elixir men edt 100 ml</t>
+  </si>
+  <si>
     <t>8715658350637</t>
   </si>
   <si>
+    <t>Omerta Hatch Eau de Toilette 100ml</t>
+  </si>
+  <si>
     <t>8715658997702</t>
   </si>
   <si>
+    <t>Real Time Cops For Men 2.0 - Eau de Toilette voor heren - 100ML</t>
+  </si>
+  <si>
     <t>8715658350620</t>
   </si>
   <si>
+    <t>Real Time Silenzia For Men - Eau de Toilette voor heren - 100ml</t>
+  </si>
+  <si>
     <t>8715658009054</t>
   </si>
   <si>
+    <t>Real Time - Call Me Black Edition - Eau de toilette - 100ML</t>
+  </si>
+  <si>
     <t>8715658350514</t>
   </si>
   <si>
+    <t>Street Looks - Wild Challenge - Eau De Toilette - 100ML</t>
+  </si>
+  <si>
     <t>8715658330004</t>
   </si>
   <si>
+    <t>Real Time Submarine Night Mission Eau de Toilette 100ml</t>
+  </si>
+  <si>
     <t>8715658350088</t>
   </si>
   <si>
+    <t>Omerta - Invasion Third Dimension - Eau De Parfum - 100Ml</t>
+  </si>
+  <si>
     <t>8715658380368</t>
   </si>
   <si>
+    <t>Street Looks - Fleurette - Eau de parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658013006</t>
   </si>
   <si>
+    <t>Real Time - Tempting Rumors - Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8715658361619</t>
   </si>
   <si>
+    <t>Real Time - Queen Of Space Blazing Sky - Eau De Parfum - 100Ml</t>
+  </si>
+  <si>
     <t>8715658360865</t>
   </si>
   <si>
+    <t>Omerta - Happy Love Fun For Women - Eau de parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658380399</t>
   </si>
   <si>
+    <t>Omerta Putting Green Eau de Toilette Pour Homme - 100ml</t>
+  </si>
+  <si>
     <t>8715658998952</t>
   </si>
   <si>
+    <t>Real Time - Smart Lady For Women - Eau de parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658360995</t>
   </si>
   <si>
+    <t>Omerta Pure E-motion Eau de Toilette 100ml</t>
+  </si>
+  <si>
     <t>8715658997436</t>
   </si>
   <si>
@@ -871,21 +1339,39 @@
     <t>8715658370215</t>
   </si>
   <si>
+    <t>Sentio May All Your Wishes Come True miniparfum eau de parfum for woman 15ml</t>
+  </si>
+  <si>
     <t>7640158817797</t>
   </si>
   <si>
+    <t>Omerta - Red Class Elixir de Luxe - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658370574</t>
   </si>
   <si>
+    <t>Real Time Queen of Space parfum - Eau de parfum voor elegante vrouwen - 100ml</t>
+  </si>
+  <si>
     <t>8715658360896</t>
   </si>
   <si>
+    <t>Real Time - Blue Touch - Eau De Toilette - 100Ml</t>
+  </si>
+  <si>
     <t>8715658350446</t>
   </si>
   <si>
+    <t>Real Time - Out Of Order - Eau De Toilette - 100ML</t>
+  </si>
+  <si>
     <t>8715658350033</t>
   </si>
   <si>
+    <t>Real Time - Night Blue Mission Pour Homme - Eau De Toilette - 100ML</t>
+  </si>
+  <si>
     <t>8715658002772</t>
   </si>
   <si>
@@ -898,12 +1384,21 @@
     <t>8715658360001</t>
   </si>
   <si>
+    <t>Vibezz Il Capitano - Eau de Toilette voor heren - 100ml</t>
+  </si>
+  <si>
     <t>7640158819241</t>
   </si>
   <si>
+    <t>Street Looks - Pure Courage - Eau de Toilette - 100ML</t>
+  </si>
+  <si>
     <t>8715658013082</t>
   </si>
   <si>
+    <t>Real Time - Me Time - Eau de Toilette - 100Ml</t>
+  </si>
+  <si>
     <t>8715658350705</t>
   </si>
   <si>
@@ -916,18 +1411,30 @@
     <t>8715658340287</t>
   </si>
   <si>
+    <t>Creation Lamis Just Perfect Dream for her - Eau de parfum met bloemige noten - 100ml</t>
+  </si>
+  <si>
     <t>5414666014427</t>
   </si>
   <si>
-    <t>1692530</t>
+    <t>Juwelium</t>
+  </si>
+  <si>
+    <t>Sentio Miniparfum Cocktail - BLUE LAGOON - Eau de parfum For Her 15ml</t>
   </si>
   <si>
     <t>7640158818763</t>
   </si>
   <si>
+    <t>Parfum SENTIO Lucky Numbers 10 You're A Ten eau de parfum 15ml</t>
+  </si>
+  <si>
     <t>8721055490357</t>
   </si>
   <si>
+    <t>NG Heaven's Smell Eau de Parfum 100 ml</t>
+  </si>
+  <si>
     <t>8718421831227</t>
   </si>
   <si>
@@ -937,6 +1444,9 @@
     <t>8721055490326</t>
   </si>
   <si>
+    <t>Hello Kitty Club Eau de Parfum voor Kinderen 50 ml - I'm the rainbow after the storm</t>
+  </si>
+  <si>
     <t>8721055493358</t>
   </si>
   <si>
@@ -949,12 +1459,21 @@
     <t>8721055498131</t>
   </si>
   <si>
+    <t>NG -Wild Men Giftset- 100ml Eau de Toilette-50ml Showergel-50ml Aftershave balm</t>
+  </si>
+  <si>
     <t>8719214757755</t>
   </si>
   <si>
+    <t>Real Time - Intense Impression For Men - Eau De Toilette - 100ML</t>
+  </si>
+  <si>
     <t>8715658350361</t>
   </si>
   <si>
+    <t>Sentio Blossy Parfum - Eau de parfum voor haar - 35ml</t>
+  </si>
+  <si>
     <t>7640158815892</t>
   </si>
   <si>
@@ -970,12 +1489,21 @@
     <t>8715658380412</t>
   </si>
   <si>
+    <t>Sentio Love &amp; Casual for Everyone Eau de Parfum Spray 100 ml</t>
+  </si>
+  <si>
     <t>8721055493747</t>
   </si>
   <si>
+    <t>NG Axure Sport Eau de Toilette 100ml</t>
+  </si>
+  <si>
     <t>8719214758325</t>
   </si>
   <si>
+    <t>Omerta - Big The Fragrance Release - Eau De Toilette - 100ML</t>
+  </si>
+  <si>
     <t>8715658370093</t>
   </si>
   <si>
@@ -985,10 +1513,16 @@
     <t>6291012874381</t>
   </si>
   <si>
+    <t>Homme for men 15ml EDT by NG</t>
+  </si>
+  <si>
     <t>8719214756031</t>
   </si>
   <si>
-    <t>1738694</t>
+    <t xml:space="preserve">Seuren Drogist Speelgoed </t>
+  </si>
+  <si>
+    <t>NG Darkness for Men Eau de Toilette 15ml</t>
   </si>
   <si>
     <t>8719214758448</t>
@@ -997,6 +1531,9 @@
     <t>8719214750848</t>
   </si>
   <si>
+    <t>Real Time - Life In Motion For Women - Eau de parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658002734</t>
   </si>
   <si>
@@ -1007,6 +1544,9 @@
   </si>
   <si>
     <t>8715658997733</t>
+  </si>
+  <si>
+    <t>Sentio Involved Pour Homme Eau de Toilette For Men 15ml</t>
   </si>
   <si>
     <t>7640158815267</t>
@@ -1445,7 +1985,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1">
         <v>24.95</v>
@@ -1457,21 +1997,21 @@
         <v>8.06</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1">
         <v>16.89</v>
       </c>
       <c r="H2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1">
         <v>24.95</v>
@@ -1483,21 +2023,21 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3" s="1">
         <v>16.95</v>
       </c>
       <c r="H3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1">
         <v>24.95</v>
@@ -1509,21 +2049,21 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G4" s="1">
         <v>16.95</v>
       </c>
       <c r="H4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1">
         <v>24.95</v>
@@ -1535,21 +2075,21 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5" s="1">
         <v>16.95</v>
       </c>
       <c r="H5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C6" s="1">
         <v>24.95</v>
@@ -1561,21 +2101,21 @@
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6" s="1">
         <v>16.95</v>
       </c>
       <c r="H6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1">
         <v>24.95</v>
@@ -1587,21 +2127,21 @@
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G7" s="1">
         <v>16.95</v>
       </c>
       <c r="H7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C8" s="1">
         <v>24.95</v>
@@ -1613,21 +2153,21 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G8" s="1">
         <v>16.95</v>
       </c>
       <c r="H8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C9" s="1">
         <v>15.95</v>
@@ -1639,21 +2179,21 @@
         <v>6.16</v>
       </c>
       <c r="F9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G9" s="1">
         <v>9.79</v>
       </c>
       <c r="H9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1">
         <v>19.95</v>
@@ -1665,21 +2205,21 @@
         <v>5.9</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G10" s="1">
         <v>14.05</v>
       </c>
       <c r="H10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C11" s="1">
         <v>19.95</v>
@@ -1691,21 +2231,21 @@
         <v>5.7</v>
       </c>
       <c r="F11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G11" s="1">
         <v>14.25</v>
       </c>
       <c r="H11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C12" s="1">
         <v>10.49</v>
@@ -1717,21 +2257,21 @@
         <v>5.5</v>
       </c>
       <c r="F12" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G12" s="1">
         <v>4.99</v>
       </c>
       <c r="H12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C13" s="1">
         <v>10.49</v>
@@ -1743,21 +2283,21 @@
         <v>5.5</v>
       </c>
       <c r="F13" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G13" s="1">
         <v>4.99</v>
       </c>
       <c r="H13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C14" s="1">
         <v>10.49</v>
@@ -1769,21 +2309,21 @@
         <v>5.5</v>
       </c>
       <c r="F14" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G14" s="1">
         <v>4.99</v>
       </c>
       <c r="H14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C15" s="1">
         <v>10.49</v>
@@ -1795,21 +2335,21 @@
         <v>5.5</v>
       </c>
       <c r="F15" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G15" s="1">
         <v>4.99</v>
       </c>
       <c r="H15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C16" s="1">
         <v>10.49</v>
@@ -1821,21 +2361,21 @@
         <v>5.5</v>
       </c>
       <c r="F16" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G16" s="1">
         <v>4.99</v>
       </c>
       <c r="H16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C17" s="1">
         <v>10.49</v>
@@ -1847,21 +2387,21 @@
         <v>5.5</v>
       </c>
       <c r="F17" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G17" s="1">
         <v>4.99</v>
       </c>
       <c r="H17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C18" s="1">
         <v>10.49</v>
@@ -1873,21 +2413,21 @@
         <v>5.5</v>
       </c>
       <c r="F18" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G18" s="1">
         <v>4.99</v>
       </c>
       <c r="H18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="C19" s="1">
         <v>10.49</v>
@@ -1899,21 +2439,21 @@
         <v>5.5</v>
       </c>
       <c r="F19" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G19" s="1">
         <v>4.99</v>
       </c>
       <c r="H19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="C20" s="1">
         <v>10.49</v>
@@ -1925,21 +2465,21 @@
         <v>5.5</v>
       </c>
       <c r="F20" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G20" s="1">
         <v>4.99</v>
       </c>
       <c r="H20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="C21" s="1">
         <v>10.49</v>
@@ -1951,21 +2491,21 @@
         <v>5.5</v>
       </c>
       <c r="F21" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G21" s="1">
         <v>4.99</v>
       </c>
       <c r="H21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="C22" s="1">
         <v>10.49</v>
@@ -1977,21 +2517,21 @@
         <v>5.5</v>
       </c>
       <c r="F22" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G22" s="1">
         <v>4.99</v>
       </c>
       <c r="H22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="C23" s="1">
         <v>10.49</v>
@@ -2003,21 +2543,21 @@
         <v>5.5</v>
       </c>
       <c r="F23" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G23" s="1">
         <v>4.99</v>
       </c>
       <c r="H23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C24" s="1">
         <v>10.49</v>
@@ -2029,21 +2569,21 @@
         <v>5.5</v>
       </c>
       <c r="F24" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G24" s="1">
         <v>4.99</v>
       </c>
       <c r="H24" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="C25" s="1">
         <v>10.49</v>
@@ -2055,21 +2595,21 @@
         <v>5.5</v>
       </c>
       <c r="F25" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G25" s="1">
         <v>4.99</v>
       </c>
       <c r="H25" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C26" s="1">
         <v>10.49</v>
@@ -2081,21 +2621,21 @@
         <v>5.5</v>
       </c>
       <c r="F26" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G26" s="1">
         <v>4.99</v>
       </c>
       <c r="H26" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="C27" s="1">
         <v>10.48</v>
@@ -2107,21 +2647,21 @@
         <v>5.49</v>
       </c>
       <c r="F27" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="G27" s="1">
         <v>4.99</v>
       </c>
       <c r="H27" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="C28" s="1">
         <v>14.95</v>
@@ -2133,21 +2673,21 @@
         <v>5.45</v>
       </c>
       <c r="F28" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="G28" s="1">
         <v>9.5</v>
       </c>
       <c r="H28" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="B29" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="C29" s="1">
         <v>14.95</v>
@@ -2159,21 +2699,21 @@
         <v>5.45</v>
       </c>
       <c r="F29" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="G29" s="1">
         <v>9.5</v>
       </c>
       <c r="H29" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="C30" s="1">
         <v>14.95</v>
@@ -2185,21 +2725,21 @@
         <v>5.45</v>
       </c>
       <c r="F30" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G30" s="1">
         <v>14.2</v>
       </c>
       <c r="H30" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="B31" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="C31" s="1">
         <v>14.95</v>
@@ -2211,21 +2751,21 @@
         <v>5.45</v>
       </c>
       <c r="F31" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="G31" s="1">
         <v>9.5</v>
       </c>
       <c r="H31" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="C32" s="1">
         <v>14.95</v>
@@ -2237,21 +2777,21 @@
         <v>5.45</v>
       </c>
       <c r="F32" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G32" s="1">
         <v>11.5</v>
       </c>
       <c r="H32" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="C33" s="1">
         <v>14.95</v>
@@ -2263,21 +2803,21 @@
         <v>5.45</v>
       </c>
       <c r="F33" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="G33" s="1">
         <v>9.5</v>
       </c>
       <c r="H33" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C34" s="1">
         <v>14.95</v>
@@ -2289,21 +2829,21 @@
         <v>5.45</v>
       </c>
       <c r="F34" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="G34" s="1">
         <v>9.5</v>
       </c>
       <c r="H34" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="C35" s="1">
         <v>14.95</v>
@@ -2315,21 +2855,21 @@
         <v>5.45</v>
       </c>
       <c r="F35" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="G35" s="1">
         <v>9.5</v>
       </c>
       <c r="H35" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="B36" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="C36" s="1">
         <v>14.95</v>
@@ -2341,21 +2881,21 @@
         <v>5.45</v>
       </c>
       <c r="F36" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="G36" s="1">
         <v>9.5</v>
       </c>
       <c r="H36" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="B37" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="C37" s="1">
         <v>14.95</v>
@@ -2367,21 +2907,21 @@
         <v>5.45</v>
       </c>
       <c r="F37" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G37" s="1">
         <v>12.66</v>
       </c>
       <c r="H37" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="B38" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="C38" s="1">
         <v>14.95</v>
@@ -2393,21 +2933,21 @@
         <v>5.45</v>
       </c>
       <c r="F38" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="G38" s="1">
         <v>9.5</v>
       </c>
       <c r="H38" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="B39" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="C39" s="1">
         <v>14.95</v>
@@ -2419,21 +2959,21 @@
         <v>5.45</v>
       </c>
       <c r="F39" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G39" s="1">
         <v>14.2</v>
       </c>
       <c r="H39" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="B40" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="C40" s="1">
         <v>14.95</v>
@@ -2445,21 +2985,21 @@
         <v>5.45</v>
       </c>
       <c r="F40" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="G40" s="1">
         <v>9.5</v>
       </c>
       <c r="H40" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="B41" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="C41" s="1">
         <v>14.95</v>
@@ -2471,21 +3011,21 @@
         <v>5.45</v>
       </c>
       <c r="F41" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="G41" s="1">
         <v>9.5</v>
       </c>
       <c r="H41" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="B42" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="C42" s="1">
         <v>14.95</v>
@@ -2497,21 +3037,21 @@
         <v>5.45</v>
       </c>
       <c r="F42" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G42" s="1">
         <v>14.2</v>
       </c>
       <c r="H42" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="B43" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="C43" s="1">
         <v>14.95</v>
@@ -2523,21 +3063,21 @@
         <v>5.45</v>
       </c>
       <c r="F43" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="G43" s="1">
         <v>9.5</v>
       </c>
       <c r="H43" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="B44" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="C44" s="1">
         <v>14.95</v>
@@ -2549,21 +3089,21 @@
         <v>5.45</v>
       </c>
       <c r="F44" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="G44" s="1">
         <v>9.5</v>
       </c>
       <c r="H44" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="B45" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="C45" s="1">
         <v>14.95</v>
@@ -2575,21 +3115,21 @@
         <v>5.45</v>
       </c>
       <c r="F45" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G45" s="1">
         <v>14.2</v>
       </c>
       <c r="H45" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="B46" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="C46" s="1">
         <v>14.95</v>
@@ -2601,21 +3141,21 @@
         <v>5.45</v>
       </c>
       <c r="F46" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="G46" s="1">
         <v>9.5</v>
       </c>
       <c r="H46" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="C47" s="1">
         <v>14.95</v>
@@ -2627,21 +3167,21 @@
         <v>5.45</v>
       </c>
       <c r="F47" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G47" s="1">
         <v>14.2</v>
       </c>
       <c r="H47" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="C48" s="1">
         <v>14.95</v>
@@ -2653,21 +3193,21 @@
         <v>5.45</v>
       </c>
       <c r="F48" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="G48" s="1">
         <v>9.5</v>
       </c>
       <c r="H48" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="B49" t="s">
-        <v>52</v>
+        <v>74</v>
       </c>
       <c r="C49" s="1">
         <v>14.95</v>
@@ -2679,21 +3219,21 @@
         <v>5.45</v>
       </c>
       <c r="F49" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G49" s="1">
         <v>14.07</v>
       </c>
       <c r="H49" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="B50" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="C50" s="1">
         <v>14.95</v>
@@ -2705,21 +3245,21 @@
         <v>5.45</v>
       </c>
       <c r="F50" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="G50" s="1">
         <v>9.5</v>
       </c>
       <c r="H50" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="B51" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="C51" s="1">
         <v>14.95</v>
@@ -2731,21 +3271,21 @@
         <v>5.45</v>
       </c>
       <c r="F51" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G51" s="1">
         <v>12.66</v>
       </c>
       <c r="H51" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="B52" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="C52" s="1">
         <v>14.95</v>
@@ -2757,21 +3297,21 @@
         <v>5.45</v>
       </c>
       <c r="F52" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="G52" s="1">
         <v>9.5</v>
       </c>
       <c r="H52" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="B53" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C53" s="1">
         <v>14.95</v>
@@ -2783,21 +3323,21 @@
         <v>5.16</v>
       </c>
       <c r="F53" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G53" s="1">
         <v>9.79</v>
       </c>
       <c r="H53" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="B54" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="C54" s="1">
         <v>14.95</v>
@@ -2809,21 +3349,21 @@
         <v>5.16</v>
       </c>
       <c r="F54" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G54" s="1">
         <v>12.5</v>
       </c>
       <c r="H54" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="B55" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="C55" s="1">
         <v>14.95</v>
@@ -2835,21 +3375,21 @@
         <v>5.16</v>
       </c>
       <c r="F55" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G55" s="1">
         <v>9.79</v>
       </c>
       <c r="H55" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="B56" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="C56" s="1">
         <v>29.95</v>
@@ -2861,21 +3401,21 @@
         <v>5</v>
       </c>
       <c r="F56" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G56" s="1">
         <v>24.95</v>
       </c>
       <c r="H56" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="B57" t="s">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="C57" s="1">
         <v>29.95</v>
@@ -2887,21 +3427,21 @@
         <v>5</v>
       </c>
       <c r="F57" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G57" s="1">
         <v>24.95</v>
       </c>
       <c r="H57" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="B58" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="C58" s="1">
         <v>29.95</v>
@@ -2913,21 +3453,21 @@
         <v>5</v>
       </c>
       <c r="F58" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G58" s="1">
         <v>24.95</v>
       </c>
       <c r="H58" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="B59" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="C59" s="1">
         <v>29.95</v>
@@ -2939,21 +3479,21 @@
         <v>5</v>
       </c>
       <c r="F59" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G59" s="1">
         <v>24.95</v>
       </c>
       <c r="H59" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="B60" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="C60" s="1">
         <v>29.95</v>
@@ -2965,21 +3505,21 @@
         <v>5</v>
       </c>
       <c r="F60" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G60" s="1">
         <v>24.95</v>
       </c>
       <c r="H60" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="B61" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="C61" s="1">
         <v>14.95</v>
@@ -2991,21 +3531,21 @@
         <v>5</v>
       </c>
       <c r="F61" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="G61" s="1">
         <v>9.95</v>
       </c>
       <c r="H61" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="B62" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="C62" s="1">
         <v>14.95</v>
@@ -3017,21 +3557,21 @@
         <v>4.96</v>
       </c>
       <c r="F62" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="G62" s="1">
         <v>9.99</v>
       </c>
       <c r="H62" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="B63" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="C63" s="1">
         <v>14.25</v>
@@ -3043,21 +3583,21 @@
         <v>4.75</v>
       </c>
       <c r="F63" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="G63" s="1">
         <v>9.5</v>
       </c>
       <c r="H63" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="B64" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="C64" s="1">
         <v>14.25</v>
@@ -3069,21 +3609,21 @@
         <v>4.75</v>
       </c>
       <c r="F64" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G64" s="1">
         <v>12.66</v>
       </c>
       <c r="H64" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="B65" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="C65" s="1">
         <v>14.25</v>
@@ -3095,21 +3635,21 @@
         <v>4.75</v>
       </c>
       <c r="F65" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="G65" s="1">
         <v>9.5</v>
       </c>
       <c r="H65" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="B66" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="C66" s="1">
         <v>14.25</v>
@@ -3121,21 +3661,21 @@
         <v>4.75</v>
       </c>
       <c r="F66" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="G66" s="1">
         <v>13.19</v>
       </c>
       <c r="H66" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="B67" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="C67" s="1">
         <v>14.25</v>
@@ -3147,21 +3687,21 @@
         <v>4.75</v>
       </c>
       <c r="F67" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G67" s="1">
         <v>14.2</v>
       </c>
       <c r="H67" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="B68" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="C68" s="1">
         <v>14.25</v>
@@ -3173,21 +3713,21 @@
         <v>4.75</v>
       </c>
       <c r="F68" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="G68" s="1">
         <v>9.5</v>
       </c>
       <c r="H68" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="B69" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="C69" s="1">
         <v>14.25</v>
@@ -3199,21 +3739,21 @@
         <v>4.75</v>
       </c>
       <c r="F69" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G69" s="1">
         <v>14.05</v>
       </c>
       <c r="H69" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="B70" t="s">
-        <v>71</v>
+        <v>99</v>
       </c>
       <c r="C70" s="1">
         <v>16.95</v>
@@ -3225,21 +3765,21 @@
         <v>4.45</v>
       </c>
       <c r="F70" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G70" s="1">
         <v>12.5</v>
       </c>
       <c r="H70" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="B71" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="C71" s="1">
         <v>14.75</v>
@@ -3251,21 +3791,21 @@
         <v>4.26</v>
       </c>
       <c r="F71" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G71" s="1">
         <v>10.49</v>
       </c>
       <c r="H71" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="B72" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="C72" s="1">
         <v>13.75</v>
@@ -3277,21 +3817,21 @@
         <v>4.25</v>
       </c>
       <c r="F72" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="G72" s="1">
         <v>9.5</v>
       </c>
       <c r="H72" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="C73" s="1">
         <v>13.75</v>
@@ -3303,21 +3843,21 @@
         <v>4.25</v>
       </c>
       <c r="F73" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="G73" s="1">
         <v>12.49</v>
       </c>
       <c r="H73" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="C74" s="1">
         <v>15.49</v>
@@ -3329,21 +3869,21 @@
         <v>3.99</v>
       </c>
       <c r="F74" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G74" s="1">
         <v>11.5</v>
       </c>
       <c r="H74" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="C75" s="1">
         <v>13.95</v>
@@ -3355,21 +3895,21 @@
         <v>3.96</v>
       </c>
       <c r="F75" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G75" s="1">
         <v>9.99</v>
       </c>
       <c r="H75" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="C76" s="1">
         <v>11.95</v>
@@ -3381,21 +3921,21 @@
         <v>3.7</v>
       </c>
       <c r="F76" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G76" s="1">
         <v>8.25</v>
       </c>
       <c r="H76" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="B77" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="C77" s="1">
         <v>11.95</v>
@@ -3407,21 +3947,21 @@
         <v>3.7</v>
       </c>
       <c r="F77" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G77" s="1">
         <v>11.5</v>
       </c>
       <c r="H77" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="B78" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="C78" s="1">
         <v>16.95</v>
@@ -3433,21 +3973,21 @@
         <v>3.54</v>
       </c>
       <c r="F78" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G78" s="1">
         <v>13.41</v>
       </c>
       <c r="H78" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="B79" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="C79" s="1">
         <v>16.95</v>
@@ -3459,21 +3999,21 @@
         <v>3.54</v>
       </c>
       <c r="F79" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G79" s="1">
         <v>15.95</v>
       </c>
       <c r="H79" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="B80" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="C80" s="1">
         <v>14.95</v>
@@ -3485,21 +4025,21 @@
         <v>3.45</v>
       </c>
       <c r="F80" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G80" s="1">
         <v>11.5</v>
       </c>
       <c r="H80" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="B81" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="C81" s="1">
         <v>14.95</v>
@@ -3511,21 +4051,21 @@
         <v>3.45</v>
       </c>
       <c r="F81" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G81" s="1">
         <v>11.5</v>
       </c>
       <c r="H81" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="B82" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="C82" s="1">
         <v>14.95</v>
@@ -3537,21 +4077,21 @@
         <v>3.45</v>
       </c>
       <c r="F82" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G82" s="1">
         <v>11.5</v>
       </c>
       <c r="H82" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="B83" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="C83" s="1">
         <v>14.95</v>
@@ -3563,21 +4103,21 @@
         <v>3.45</v>
       </c>
       <c r="F83" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G83" s="1">
         <v>11.5</v>
       </c>
       <c r="H83" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="B84" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="C84" s="1">
         <v>14.95</v>
@@ -3589,21 +4129,21 @@
         <v>3.45</v>
       </c>
       <c r="F84" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G84" s="1">
         <v>11.5</v>
       </c>
       <c r="H84" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="B85" t="s">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="C85" s="1">
         <v>12.95</v>
@@ -3615,21 +4155,21 @@
         <v>3.45</v>
       </c>
       <c r="F85" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="G85" s="1">
         <v>9.5</v>
       </c>
       <c r="H85" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="B86" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="C86" s="1">
         <v>14.95</v>
@@ -3641,21 +4181,21 @@
         <v>3.45</v>
       </c>
       <c r="F86" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G86" s="1">
         <v>11.5</v>
       </c>
       <c r="H86" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="B87" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="C87" s="1">
         <v>14.95</v>
@@ -3667,21 +4207,21 @@
         <v>3.45</v>
       </c>
       <c r="F87" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G87" s="1">
         <v>12.5</v>
       </c>
       <c r="H87" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="B88" t="s">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="C88" s="1">
         <v>17.95</v>
@@ -3693,21 +4233,21 @@
         <v>3.2</v>
       </c>
       <c r="F88" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G88" s="1">
         <v>14.75</v>
       </c>
       <c r="H88" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="B89" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="C89" s="1">
         <v>14.95</v>
@@ -3719,21 +4259,21 @@
         <v>3.2</v>
       </c>
       <c r="F89" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G89" s="1">
         <v>11.75</v>
       </c>
       <c r="H89" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="B90" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="C90" s="1">
         <v>14.95</v>
@@ -3745,21 +4285,21 @@
         <v>3.2</v>
       </c>
       <c r="F90" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G90" s="1">
         <v>12.5</v>
       </c>
       <c r="H90" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="B91" t="s">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="C91" s="1">
         <v>17.95</v>
@@ -3771,21 +4311,21 @@
         <v>3.2</v>
       </c>
       <c r="F91" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G91" s="1">
         <v>14.75</v>
       </c>
       <c r="H91" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="B92" t="s">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="C92" s="1">
         <v>14.95</v>
@@ -3797,21 +4337,21 @@
         <v>3.2</v>
       </c>
       <c r="F92" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G92" s="1">
         <v>11.75</v>
       </c>
       <c r="H92" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>89</v>
+        <v>126</v>
       </c>
       <c r="B93" t="s">
-        <v>89</v>
+        <v>127</v>
       </c>
       <c r="C93" s="1">
         <v>14.95</v>
@@ -3823,21 +4363,21 @@
         <v>3.2</v>
       </c>
       <c r="F93" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G93" s="1">
         <v>11.75</v>
       </c>
       <c r="H93" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="B94" t="s">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="C94" s="1">
         <v>14.95</v>
@@ -3849,21 +4389,21 @@
         <v>3.2</v>
       </c>
       <c r="F94" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G94" s="1">
         <v>11.75</v>
       </c>
       <c r="H94" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="B95" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="C95" s="1">
         <v>14.95</v>
@@ -3875,21 +4415,21 @@
         <v>3.2</v>
       </c>
       <c r="F95" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G95" s="1">
         <v>11.75</v>
       </c>
       <c r="H95" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="B96" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="C96" s="1">
         <v>14.95</v>
@@ -3901,21 +4441,21 @@
         <v>3.2</v>
       </c>
       <c r="F96" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G96" s="1">
         <v>11.75</v>
       </c>
       <c r="H96" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>93</v>
+        <v>132</v>
       </c>
       <c r="B97" t="s">
-        <v>93</v>
+        <v>132</v>
       </c>
       <c r="C97" s="1">
         <v>17.95</v>
@@ -3927,21 +4467,21 @@
         <v>3.2</v>
       </c>
       <c r="F97" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G97" s="1">
         <v>14.75</v>
       </c>
       <c r="H97" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="B98" t="s">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="C98" s="1">
         <v>17.95</v>
@@ -3953,21 +4493,21 @@
         <v>3.2</v>
       </c>
       <c r="F98" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G98" s="1">
         <v>14.75</v>
       </c>
       <c r="H98" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>95</v>
+        <v>134</v>
       </c>
       <c r="B99" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="C99" s="1">
         <v>14.95</v>
@@ -3979,21 +4519,21 @@
         <v>3</v>
       </c>
       <c r="F99" t="s">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="G99" s="1">
         <v>11.95</v>
       </c>
       <c r="H99" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="B100" t="s">
-        <v>97</v>
+        <v>138</v>
       </c>
       <c r="C100" s="1">
         <v>14.95</v>
@@ -4005,21 +4545,21 @@
         <v>2.76</v>
       </c>
       <c r="F100" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="G100" s="1">
         <v>12.19</v>
       </c>
       <c r="H100" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="B101" t="s">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="C101" s="1">
         <v>14.95</v>
@@ -4031,21 +4571,21 @@
         <v>2.76</v>
       </c>
       <c r="F101" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="G101" s="1">
         <v>12.19</v>
       </c>
       <c r="H101" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="B102" t="s">
-        <v>99</v>
+        <v>141</v>
       </c>
       <c r="C102" s="1">
         <v>14.95</v>
@@ -4057,21 +4597,21 @@
         <v>2.73</v>
       </c>
       <c r="F102" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G102" s="1">
         <v>12.22</v>
       </c>
       <c r="H102" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="B103" t="s">
-        <v>100</v>
+        <v>143</v>
       </c>
       <c r="C103" s="1">
         <v>10.49</v>
@@ -4083,21 +4623,21 @@
         <v>2.5</v>
       </c>
       <c r="F103" t="s">
-        <v>101</v>
+        <v>144</v>
       </c>
       <c r="G103" s="1">
         <v>7.99</v>
       </c>
       <c r="H103" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>102</v>
+        <v>145</v>
       </c>
       <c r="B104" t="s">
-        <v>102</v>
+        <v>145</v>
       </c>
       <c r="C104" s="1">
         <v>10.99</v>
@@ -4109,21 +4649,21 @@
         <v>2.49</v>
       </c>
       <c r="F104" t="s">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="G104" s="1">
         <v>8.5</v>
       </c>
       <c r="H104" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>104</v>
+        <v>147</v>
       </c>
       <c r="B105" t="s">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="C105" s="1">
         <v>14.95</v>
@@ -4135,21 +4675,21 @@
         <v>2.45</v>
       </c>
       <c r="F105" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G105" s="1">
         <v>12.5</v>
       </c>
       <c r="H105" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>105</v>
+        <v>149</v>
       </c>
       <c r="B106" t="s">
-        <v>105</v>
+        <v>150</v>
       </c>
       <c r="C106" s="1">
         <v>14.95</v>
@@ -4161,21 +4701,21 @@
         <v>2.45</v>
       </c>
       <c r="F106" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G106" s="1">
         <v>12.5</v>
       </c>
       <c r="H106" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>106</v>
+        <v>151</v>
       </c>
       <c r="B107" t="s">
-        <v>106</v>
+        <v>152</v>
       </c>
       <c r="C107" s="1">
         <v>14.95</v>
@@ -4187,21 +4727,21 @@
         <v>2.45</v>
       </c>
       <c r="F107" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G107" s="1">
         <v>12.5</v>
       </c>
       <c r="H107" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>107</v>
+        <v>153</v>
       </c>
       <c r="B108" t="s">
-        <v>107</v>
+        <v>154</v>
       </c>
       <c r="C108" s="1">
         <v>14.95</v>
@@ -4213,21 +4753,21 @@
         <v>2.45</v>
       </c>
       <c r="F108" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G108" s="1">
         <v>12.5</v>
       </c>
       <c r="H108" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c r="B109" t="s">
-        <v>108</v>
+        <v>156</v>
       </c>
       <c r="C109" s="1">
         <v>14.95</v>
@@ -4239,21 +4779,21 @@
         <v>2.45</v>
       </c>
       <c r="F109" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G109" s="1">
         <v>12.5</v>
       </c>
       <c r="H109" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>109</v>
+        <v>157</v>
       </c>
       <c r="B110" t="s">
-        <v>109</v>
+        <v>158</v>
       </c>
       <c r="C110" s="1">
         <v>14.95</v>
@@ -4265,21 +4805,21 @@
         <v>2.45</v>
       </c>
       <c r="F110" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G110" s="1">
         <v>12.5</v>
       </c>
       <c r="H110" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>109</v>
+        <v>157</v>
       </c>
       <c r="B111" t="s">
-        <v>109</v>
+        <v>158</v>
       </c>
       <c r="C111" s="1">
         <v>14.95</v>
@@ -4291,21 +4831,21 @@
         <v>2.45</v>
       </c>
       <c r="F111" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G111" s="1">
         <v>14.78</v>
       </c>
       <c r="H111" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>110</v>
+        <v>159</v>
       </c>
       <c r="B112" t="s">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="C112" s="1">
         <v>14.95</v>
@@ -4317,21 +4857,21 @@
         <v>2.45</v>
       </c>
       <c r="F112" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G112" s="1">
         <v>12.5</v>
       </c>
       <c r="H112" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>111</v>
+        <v>161</v>
       </c>
       <c r="B113" t="s">
-        <v>111</v>
+        <v>162</v>
       </c>
       <c r="C113" s="1">
         <v>14.95</v>
@@ -4343,21 +4883,21 @@
         <v>2.45</v>
       </c>
       <c r="F113" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G113" s="1">
         <v>12.5</v>
       </c>
       <c r="H113" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="B114" t="s">
-        <v>112</v>
+        <v>164</v>
       </c>
       <c r="C114" s="1">
         <v>14.95</v>
@@ -4369,21 +4909,21 @@
         <v>2.45</v>
       </c>
       <c r="F114" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G114" s="1">
         <v>12.5</v>
       </c>
       <c r="H114" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>113</v>
+        <v>165</v>
       </c>
       <c r="B115" t="s">
-        <v>113</v>
+        <v>166</v>
       </c>
       <c r="C115" s="1">
         <v>16.95</v>
@@ -4395,21 +4935,21 @@
         <v>2.45</v>
       </c>
       <c r="F115" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G115" s="1">
         <v>14.5</v>
       </c>
       <c r="H115" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>114</v>
+        <v>167</v>
       </c>
       <c r="B116" t="s">
-        <v>114</v>
+        <v>168</v>
       </c>
       <c r="C116" s="1">
         <v>14.95</v>
@@ -4421,21 +4961,21 @@
         <v>2.45</v>
       </c>
       <c r="F116" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G116" s="1">
         <v>12.5</v>
       </c>
       <c r="H116" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>115</v>
+        <v>169</v>
       </c>
       <c r="B117" t="s">
-        <v>115</v>
+        <v>170</v>
       </c>
       <c r="C117" s="1">
         <v>14.95</v>
@@ -4447,21 +4987,21 @@
         <v>2.45</v>
       </c>
       <c r="F117" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G117" s="1">
         <v>12.5</v>
       </c>
       <c r="H117" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>116</v>
+        <v>171</v>
       </c>
       <c r="B118" t="s">
-        <v>116</v>
+        <v>172</v>
       </c>
       <c r="C118" s="1">
         <v>14.95</v>
@@ -4473,21 +5013,21 @@
         <v>2.45</v>
       </c>
       <c r="F118" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G118" s="1">
         <v>12.5</v>
       </c>
       <c r="H118" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>117</v>
+        <v>173</v>
       </c>
       <c r="B119" t="s">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="C119" s="1">
         <v>14.95</v>
@@ -4499,21 +5039,21 @@
         <v>2.45</v>
       </c>
       <c r="F119" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G119" s="1">
         <v>12.5</v>
       </c>
       <c r="H119" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>118</v>
+        <v>175</v>
       </c>
       <c r="B120" t="s">
-        <v>118</v>
+        <v>176</v>
       </c>
       <c r="C120" s="1">
         <v>14.95</v>
@@ -4525,21 +5065,21 @@
         <v>2.45</v>
       </c>
       <c r="F120" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G120" s="1">
         <v>12.5</v>
       </c>
       <c r="H120" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>119</v>
+        <v>177</v>
       </c>
       <c r="B121" t="s">
-        <v>119</v>
+        <v>178</v>
       </c>
       <c r="C121" s="1">
         <v>14.95</v>
@@ -4551,21 +5091,21 @@
         <v>2.45</v>
       </c>
       <c r="F121" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G121" s="1">
         <v>12.5</v>
       </c>
       <c r="H121" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="B122" t="s">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="C122" s="1">
         <v>14.95</v>
@@ -4577,21 +5117,21 @@
         <v>2.45</v>
       </c>
       <c r="F122" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G122" s="1">
         <v>12.5</v>
       </c>
       <c r="H122" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>121</v>
+        <v>181</v>
       </c>
       <c r="B123" t="s">
-        <v>121</v>
+        <v>182</v>
       </c>
       <c r="C123" s="1">
         <v>14.95</v>
@@ -4603,21 +5143,21 @@
         <v>2.45</v>
       </c>
       <c r="F123" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G123" s="1">
         <v>12.5</v>
       </c>
       <c r="H123" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>121</v>
+        <v>181</v>
       </c>
       <c r="B124" t="s">
-        <v>121</v>
+        <v>182</v>
       </c>
       <c r="C124" s="1">
         <v>14.95</v>
@@ -4629,21 +5169,21 @@
         <v>2.45</v>
       </c>
       <c r="F124" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G124" s="1">
         <v>14.2</v>
       </c>
       <c r="H124" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>122</v>
+        <v>183</v>
       </c>
       <c r="B125" t="s">
-        <v>122</v>
+        <v>184</v>
       </c>
       <c r="C125" s="1">
         <v>14.95</v>
@@ -4655,21 +5195,21 @@
         <v>2.45</v>
       </c>
       <c r="F125" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G125" s="1">
         <v>12.5</v>
       </c>
       <c r="H125" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>123</v>
+        <v>185</v>
       </c>
       <c r="B126" t="s">
-        <v>123</v>
+        <v>186</v>
       </c>
       <c r="C126" s="1">
         <v>14.95</v>
@@ -4681,21 +5221,21 @@
         <v>2.45</v>
       </c>
       <c r="F126" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G126" s="1">
         <v>12.5</v>
       </c>
       <c r="H126" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>124</v>
+        <v>187</v>
       </c>
       <c r="B127" t="s">
-        <v>124</v>
+        <v>188</v>
       </c>
       <c r="C127" s="1">
         <v>14.95</v>
@@ -4707,21 +5247,21 @@
         <v>2.45</v>
       </c>
       <c r="F127" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G127" s="1">
         <v>12.5</v>
       </c>
       <c r="H127" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>125</v>
+        <v>189</v>
       </c>
       <c r="B128" t="s">
-        <v>125</v>
+        <v>190</v>
       </c>
       <c r="C128" s="1">
         <v>14.95</v>
@@ -4733,21 +5273,21 @@
         <v>2.45</v>
       </c>
       <c r="F128" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G128" s="1">
         <v>12.5</v>
       </c>
       <c r="H128" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>126</v>
+        <v>191</v>
       </c>
       <c r="B129" t="s">
-        <v>126</v>
+        <v>192</v>
       </c>
       <c r="C129" s="1">
         <v>14.95</v>
@@ -4759,21 +5299,21 @@
         <v>2.45</v>
       </c>
       <c r="F129" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G129" s="1">
         <v>12.5</v>
       </c>
       <c r="H129" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>126</v>
+        <v>191</v>
       </c>
       <c r="B130" t="s">
-        <v>126</v>
+        <v>192</v>
       </c>
       <c r="C130" s="1">
         <v>14.95</v>
@@ -4785,21 +5325,21 @@
         <v>2.45</v>
       </c>
       <c r="F130" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G130" s="1">
         <v>14.2</v>
       </c>
       <c r="H130" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>127</v>
+        <v>193</v>
       </c>
       <c r="B131" t="s">
-        <v>127</v>
+        <v>194</v>
       </c>
       <c r="C131" s="1">
         <v>14.95</v>
@@ -4811,21 +5351,21 @@
         <v>2.45</v>
       </c>
       <c r="F131" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G131" s="1">
         <v>12.5</v>
       </c>
       <c r="H131" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>127</v>
+        <v>193</v>
       </c>
       <c r="B132" t="s">
-        <v>127</v>
+        <v>194</v>
       </c>
       <c r="C132" s="1">
         <v>14.95</v>
@@ -4837,21 +5377,21 @@
         <v>2.45</v>
       </c>
       <c r="F132" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G132" s="1">
         <v>14.2</v>
       </c>
       <c r="H132" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>128</v>
+        <v>195</v>
       </c>
       <c r="B133" t="s">
-        <v>128</v>
+        <v>195</v>
       </c>
       <c r="C133" s="1">
         <v>16.95</v>
@@ -4863,21 +5403,21 @@
         <v>2.45</v>
       </c>
       <c r="F133" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G133" s="1">
         <v>14.5</v>
       </c>
       <c r="H133" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>129</v>
+        <v>196</v>
       </c>
       <c r="B134" t="s">
-        <v>129</v>
+        <v>196</v>
       </c>
       <c r="C134" s="1">
         <v>14.95</v>
@@ -4889,21 +5429,21 @@
         <v>2.45</v>
       </c>
       <c r="F134" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G134" s="1">
         <v>12.5</v>
       </c>
       <c r="H134" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>130</v>
+        <v>197</v>
       </c>
       <c r="B135" t="s">
-        <v>130</v>
+        <v>197</v>
       </c>
       <c r="C135" s="1">
         <v>14.95</v>
@@ -4915,21 +5455,21 @@
         <v>2.45</v>
       </c>
       <c r="F135" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G135" s="1">
         <v>12.5</v>
       </c>
       <c r="H135" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>131</v>
+        <v>198</v>
       </c>
       <c r="B136" t="s">
-        <v>131</v>
+        <v>198</v>
       </c>
       <c r="C136" s="1">
         <v>13.95</v>
@@ -4941,21 +5481,21 @@
         <v>2.45</v>
       </c>
       <c r="F136" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G136" s="1">
         <v>11.5</v>
       </c>
       <c r="H136" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>132</v>
+        <v>199</v>
       </c>
       <c r="B137" t="s">
-        <v>132</v>
+        <v>199</v>
       </c>
       <c r="C137" s="1">
         <v>14.95</v>
@@ -4967,21 +5507,21 @@
         <v>2.45</v>
       </c>
       <c r="F137" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G137" s="1">
         <v>12.5</v>
       </c>
       <c r="H137" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>133</v>
+        <v>200</v>
       </c>
       <c r="B138" t="s">
-        <v>133</v>
+        <v>200</v>
       </c>
       <c r="C138" s="1">
         <v>14.95</v>
@@ -4993,21 +5533,21 @@
         <v>2.45</v>
       </c>
       <c r="F138" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G138" s="1">
         <v>12.5</v>
       </c>
       <c r="H138" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>134</v>
+        <v>201</v>
       </c>
       <c r="B139" t="s">
-        <v>134</v>
+        <v>201</v>
       </c>
       <c r="C139" s="1">
         <v>14.95</v>
@@ -5019,21 +5559,21 @@
         <v>2.45</v>
       </c>
       <c r="F139" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G139" s="1">
         <v>12.5</v>
       </c>
       <c r="H139" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>135</v>
+        <v>202</v>
       </c>
       <c r="B140" t="s">
-        <v>135</v>
+        <v>202</v>
       </c>
       <c r="C140" s="1">
         <v>16.95</v>
@@ -5045,21 +5585,21 @@
         <v>2.45</v>
       </c>
       <c r="F140" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G140" s="1">
         <v>14.5</v>
       </c>
       <c r="H140" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>136</v>
+        <v>203</v>
       </c>
       <c r="B141" t="s">
-        <v>136</v>
+        <v>203</v>
       </c>
       <c r="C141" s="1">
         <v>14.95</v>
@@ -5071,21 +5611,21 @@
         <v>2.45</v>
       </c>
       <c r="F141" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G141" s="1">
         <v>12.5</v>
       </c>
       <c r="H141" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>136</v>
+        <v>203</v>
       </c>
       <c r="B142" t="s">
-        <v>136</v>
+        <v>203</v>
       </c>
       <c r="C142" s="1">
         <v>14.95</v>
@@ -5097,21 +5637,21 @@
         <v>2.45</v>
       </c>
       <c r="F142" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G142" s="1">
         <v>14.07</v>
       </c>
       <c r="H142" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>137</v>
+        <v>204</v>
       </c>
       <c r="B143" t="s">
-        <v>137</v>
+        <v>204</v>
       </c>
       <c r="C143" s="1">
         <v>14.95</v>
@@ -5123,21 +5663,21 @@
         <v>2.45</v>
       </c>
       <c r="F143" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G143" s="1">
         <v>12.5</v>
       </c>
       <c r="H143" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>138</v>
+        <v>205</v>
       </c>
       <c r="B144" t="s">
-        <v>138</v>
+        <v>205</v>
       </c>
       <c r="C144" s="1">
         <v>14.95</v>
@@ -5149,21 +5689,21 @@
         <v>2.45</v>
       </c>
       <c r="F144" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G144" s="1">
         <v>12.5</v>
       </c>
       <c r="H144" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>138</v>
+        <v>205</v>
       </c>
       <c r="B145" t="s">
-        <v>138</v>
+        <v>205</v>
       </c>
       <c r="C145" s="1">
         <v>14.95</v>
@@ -5175,21 +5715,21 @@
         <v>2.45</v>
       </c>
       <c r="F145" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G145" s="1">
         <v>14.2</v>
       </c>
       <c r="H145" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>139</v>
+        <v>206</v>
       </c>
       <c r="B146" t="s">
-        <v>139</v>
+        <v>206</v>
       </c>
       <c r="C146" s="1">
         <v>14.95</v>
@@ -5201,21 +5741,21 @@
         <v>2.45</v>
       </c>
       <c r="F146" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G146" s="1">
         <v>12.5</v>
       </c>
       <c r="H146" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>139</v>
+        <v>206</v>
       </c>
       <c r="B147" t="s">
-        <v>139</v>
+        <v>206</v>
       </c>
       <c r="C147" s="1">
         <v>14.95</v>
@@ -5227,21 +5767,21 @@
         <v>2.45</v>
       </c>
       <c r="F147" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G147" s="1">
         <v>14.78</v>
       </c>
       <c r="H147" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>140</v>
+        <v>207</v>
       </c>
       <c r="B148" t="s">
-        <v>140</v>
+        <v>207</v>
       </c>
       <c r="C148" s="1">
         <v>14.95</v>
@@ -5253,21 +5793,21 @@
         <v>2.45</v>
       </c>
       <c r="F148" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G148" s="1">
         <v>12.5</v>
       </c>
       <c r="H148" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>141</v>
+        <v>208</v>
       </c>
       <c r="B149" t="s">
-        <v>141</v>
+        <v>208</v>
       </c>
       <c r="C149" s="1">
         <v>14.95</v>
@@ -5279,21 +5819,21 @@
         <v>2.45</v>
       </c>
       <c r="F149" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G149" s="1">
         <v>12.5</v>
       </c>
       <c r="H149" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="B150" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="C150" s="1">
         <v>14.95</v>
@@ -5305,21 +5845,21 @@
         <v>2.45</v>
       </c>
       <c r="F150" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G150" s="1">
         <v>12.5</v>
       </c>
       <c r="H150" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>143</v>
+        <v>210</v>
       </c>
       <c r="B151" t="s">
-        <v>143</v>
+        <v>210</v>
       </c>
       <c r="C151" s="1">
         <v>14.95</v>
@@ -5331,21 +5871,21 @@
         <v>2.45</v>
       </c>
       <c r="F151" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G151" s="1">
         <v>12.5</v>
       </c>
       <c r="H151" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>143</v>
+        <v>210</v>
       </c>
       <c r="B152" t="s">
-        <v>143</v>
+        <v>210</v>
       </c>
       <c r="C152" s="1">
         <v>14.95</v>
@@ -5357,21 +5897,21 @@
         <v>2.45</v>
       </c>
       <c r="F152" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G152" s="1">
         <v>12.66</v>
       </c>
       <c r="H152" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>144</v>
+        <v>211</v>
       </c>
       <c r="B153" t="s">
-        <v>144</v>
+        <v>211</v>
       </c>
       <c r="C153" s="1">
         <v>14.95</v>
@@ -5383,21 +5923,21 @@
         <v>2.45</v>
       </c>
       <c r="F153" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G153" s="1">
         <v>12.5</v>
       </c>
       <c r="H153" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>144</v>
+        <v>211</v>
       </c>
       <c r="B154" t="s">
-        <v>144</v>
+        <v>211</v>
       </c>
       <c r="C154" s="1">
         <v>14.95</v>
@@ -5409,21 +5949,21 @@
         <v>2.45</v>
       </c>
       <c r="F154" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G154" s="1">
         <v>14.2</v>
       </c>
       <c r="H154" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>145</v>
+        <v>212</v>
       </c>
       <c r="B155" t="s">
-        <v>145</v>
+        <v>213</v>
       </c>
       <c r="C155" s="1">
         <v>14.95</v>
@@ -5435,21 +5975,21 @@
         <v>2.29</v>
       </c>
       <c r="F155" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G155" s="1">
         <v>12.66</v>
       </c>
       <c r="H155" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>146</v>
+        <v>214</v>
       </c>
       <c r="B156" t="s">
-        <v>146</v>
+        <v>214</v>
       </c>
       <c r="C156" s="1">
         <v>14.95</v>
@@ -5461,21 +6001,21 @@
         <v>2.29</v>
       </c>
       <c r="F156" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G156" s="1">
         <v>12.66</v>
       </c>
       <c r="H156" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>147</v>
+        <v>215</v>
       </c>
       <c r="B157" t="s">
-        <v>147</v>
+        <v>215</v>
       </c>
       <c r="C157" s="1">
         <v>14.95</v>
@@ -5487,73 +6027,73 @@
         <v>2.29</v>
       </c>
       <c r="F157" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G157" s="1">
         <v>12.66</v>
       </c>
       <c r="H157" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>148</v>
+        <v>216</v>
       </c>
       <c r="B158" t="s">
-        <v>148</v>
+        <v>216</v>
       </c>
       <c r="C158" s="1">
-        <v>14.75</v>
+        <v>14.95</v>
       </c>
       <c r="D158" s="1">
-        <v>12.5</v>
+        <v>12.66</v>
       </c>
       <c r="E158" s="1">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="F158" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G158" s="1">
-        <v>12.5</v>
+        <v>12.66</v>
       </c>
       <c r="H158" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>149</v>
+        <v>217</v>
       </c>
       <c r="B159" t="s">
-        <v>149</v>
+        <v>217</v>
       </c>
       <c r="C159" s="1">
-        <v>14.95</v>
+        <v>14.75</v>
       </c>
       <c r="D159" s="1">
-        <v>12.72</v>
+        <v>12.5</v>
       </c>
       <c r="E159" s="1">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="F159" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="G159" s="1">
-        <v>12.72</v>
+        <v>12.5</v>
       </c>
       <c r="H159" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>150</v>
+        <v>218</v>
       </c>
       <c r="B160" t="s">
-        <v>150</v>
+        <v>219</v>
       </c>
       <c r="C160" s="1">
         <v>10.49</v>
@@ -5565,21 +6105,21 @@
         <v>2.2</v>
       </c>
       <c r="F160" t="s">
-        <v>101</v>
+        <v>144</v>
       </c>
       <c r="G160" s="1">
         <v>8.29</v>
       </c>
       <c r="H160" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="B161" t="s">
-        <v>151</v>
+        <v>220</v>
       </c>
       <c r="C161" s="1">
         <v>13.69</v>
@@ -5591,21 +6131,21 @@
         <v>2.19</v>
       </c>
       <c r="F161" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G161" s="1">
         <v>11.5</v>
       </c>
       <c r="H161" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>152</v>
+        <v>221</v>
       </c>
       <c r="B162" t="s">
-        <v>152</v>
+        <v>222</v>
       </c>
       <c r="C162" s="1">
         <v>14.25</v>
@@ -5617,21 +6157,21 @@
         <v>2.06</v>
       </c>
       <c r="F162" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="G162" s="1">
         <v>12.19</v>
       </c>
       <c r="H162" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>153</v>
+        <v>223</v>
       </c>
       <c r="B163" t="s">
-        <v>153</v>
+        <v>224</v>
       </c>
       <c r="C163" s="1">
         <v>17.95</v>
@@ -5643,21 +6183,21 @@
         <v>2</v>
       </c>
       <c r="F163" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G163" s="1">
         <v>15.95</v>
       </c>
       <c r="H163" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>154</v>
+        <v>225</v>
       </c>
       <c r="B164" t="s">
-        <v>154</v>
+        <v>226</v>
       </c>
       <c r="C164" s="1">
         <v>10.49</v>
@@ -5669,21 +6209,21 @@
         <v>2</v>
       </c>
       <c r="F164" t="s">
-        <v>155</v>
+        <v>227</v>
       </c>
       <c r="G164" s="1">
         <v>8.49</v>
       </c>
       <c r="H164" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>156</v>
+        <v>228</v>
       </c>
       <c r="B165" t="s">
-        <v>156</v>
+        <v>229</v>
       </c>
       <c r="C165" s="1">
         <v>16.95</v>
@@ -5695,21 +6235,21 @@
         <v>2</v>
       </c>
       <c r="F165" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G165" s="1">
         <v>14.95</v>
       </c>
       <c r="H165" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>157</v>
+        <v>230</v>
       </c>
       <c r="B166" t="s">
-        <v>157</v>
+        <v>231</v>
       </c>
       <c r="C166" s="1">
         <v>13.5</v>
@@ -5721,21 +6261,21 @@
         <v>2</v>
       </c>
       <c r="F166" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G166" s="1">
         <v>11.5</v>
       </c>
       <c r="H166" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>157</v>
+        <v>230</v>
       </c>
       <c r="B167" t="s">
-        <v>157</v>
+        <v>231</v>
       </c>
       <c r="C167" s="1">
         <v>13.5</v>
@@ -5747,21 +6287,21 @@
         <v>2</v>
       </c>
       <c r="F167" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G167" s="1">
         <v>12.66</v>
       </c>
       <c r="H167" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>158</v>
+        <v>232</v>
       </c>
       <c r="B168" t="s">
-        <v>158</v>
+        <v>233</v>
       </c>
       <c r="C168" s="1">
         <v>16.95</v>
@@ -5773,21 +6313,21 @@
         <v>2</v>
       </c>
       <c r="F168" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G168" s="1">
         <v>14.95</v>
       </c>
       <c r="H168" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>159</v>
+        <v>234</v>
       </c>
       <c r="B169" t="s">
-        <v>159</v>
+        <v>235</v>
       </c>
       <c r="C169" s="1">
         <v>9.99</v>
@@ -5799,21 +6339,21 @@
         <v>2</v>
       </c>
       <c r="F169" t="s">
-        <v>101</v>
+        <v>144</v>
       </c>
       <c r="G169" s="1">
         <v>7.99</v>
       </c>
       <c r="H169" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>160</v>
+        <v>236</v>
       </c>
       <c r="B170" t="s">
-        <v>160</v>
+        <v>237</v>
       </c>
       <c r="C170" s="1">
         <v>14.95</v>
@@ -5825,21 +6365,21 @@
         <v>2</v>
       </c>
       <c r="F170" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="G170" s="1">
         <v>12.95</v>
       </c>
       <c r="H170" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>161</v>
+        <v>238</v>
       </c>
       <c r="B171" t="s">
-        <v>161</v>
+        <v>239</v>
       </c>
       <c r="C171" s="1">
         <v>16.95</v>
@@ -5851,21 +6391,21 @@
         <v>2</v>
       </c>
       <c r="F171" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G171" s="1">
         <v>14.95</v>
       </c>
       <c r="H171" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>162</v>
+        <v>240</v>
       </c>
       <c r="B172" t="s">
-        <v>162</v>
+        <v>241</v>
       </c>
       <c r="C172" s="1">
         <v>10.49</v>
@@ -5877,21 +6417,21 @@
         <v>1.99</v>
       </c>
       <c r="F172" t="s">
-        <v>101</v>
+        <v>144</v>
       </c>
       <c r="G172" s="1">
         <v>8.5</v>
       </c>
       <c r="H172" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>163</v>
+        <v>242</v>
       </c>
       <c r="B173" t="s">
-        <v>163</v>
+        <v>243</v>
       </c>
       <c r="C173" s="1">
         <v>10.49</v>
@@ -5903,21 +6443,21 @@
         <v>1.99</v>
       </c>
       <c r="F173" t="s">
-        <v>101</v>
+        <v>144</v>
       </c>
       <c r="G173" s="1">
         <v>8.5</v>
       </c>
       <c r="H173" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>164</v>
+        <v>244</v>
       </c>
       <c r="B174" t="s">
-        <v>164</v>
+        <v>245</v>
       </c>
       <c r="C174" s="1">
         <v>9.95</v>
@@ -5929,21 +6469,21 @@
         <v>1.96</v>
       </c>
       <c r="F174" t="s">
-        <v>165</v>
+        <v>246</v>
       </c>
       <c r="G174" s="1">
         <v>7.99</v>
       </c>
       <c r="H174" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>166</v>
+        <v>247</v>
       </c>
       <c r="B175" t="s">
-        <v>166</v>
+        <v>248</v>
       </c>
       <c r="C175" s="1">
         <v>9.95</v>
@@ -5955,21 +6495,21 @@
         <v>1.96</v>
       </c>
       <c r="F175" t="s">
-        <v>165</v>
+        <v>246</v>
       </c>
       <c r="G175" s="1">
         <v>7.99</v>
       </c>
       <c r="H175" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>167</v>
+        <v>249</v>
       </c>
       <c r="B176" t="s">
-        <v>167</v>
+        <v>249</v>
       </c>
       <c r="C176" s="1">
         <v>14.95</v>
@@ -5981,21 +6521,21 @@
         <v>1.96</v>
       </c>
       <c r="F176" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="G176" s="1">
         <v>12.99</v>
       </c>
       <c r="H176" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>167</v>
+        <v>249</v>
       </c>
       <c r="B177" t="s">
-        <v>167</v>
+        <v>249</v>
       </c>
       <c r="C177" s="1">
         <v>14.95</v>
@@ -6007,21 +6547,21 @@
         <v>1.96</v>
       </c>
       <c r="F177" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G177" s="1">
         <v>14.2</v>
       </c>
       <c r="H177" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>168</v>
+        <v>250</v>
       </c>
       <c r="B178" t="s">
-        <v>168</v>
+        <v>250</v>
       </c>
       <c r="C178" s="1">
         <v>17.95</v>
@@ -6033,21 +6573,21 @@
         <v>1.96</v>
       </c>
       <c r="F178" t="s">
-        <v>169</v>
+        <v>251</v>
       </c>
       <c r="G178" s="1">
         <v>15.99</v>
       </c>
       <c r="H178" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>170</v>
+        <v>252</v>
       </c>
       <c r="B179" t="s">
-        <v>170</v>
+        <v>253</v>
       </c>
       <c r="C179" s="1">
         <v>14.95</v>
@@ -6059,21 +6599,21 @@
         <v>1.91</v>
       </c>
       <c r="F179" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G179" s="1">
         <v>13.04</v>
       </c>
       <c r="H179" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>171</v>
+        <v>254</v>
       </c>
       <c r="B180" t="s">
-        <v>171</v>
+        <v>255</v>
       </c>
       <c r="C180" s="1">
         <v>10.49</v>
@@ -6085,21 +6625,21 @@
         <v>1.81</v>
       </c>
       <c r="F180" t="s">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="G180" s="1">
         <v>8.68</v>
       </c>
       <c r="H180" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>172</v>
+        <v>256</v>
       </c>
       <c r="B181" t="s">
-        <v>172</v>
+        <v>257</v>
       </c>
       <c r="C181" s="1">
         <v>17.75</v>
@@ -6111,21 +6651,21 @@
         <v>1.8</v>
       </c>
       <c r="F181" t="s">
-        <v>173</v>
+        <v>258</v>
       </c>
       <c r="G181" s="1">
         <v>15.95</v>
       </c>
       <c r="H181" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>174</v>
+        <v>259</v>
       </c>
       <c r="B182" t="s">
-        <v>174</v>
+        <v>260</v>
       </c>
       <c r="C182" s="1">
         <v>14.95</v>
@@ -6137,21 +6677,21 @@
         <v>1.79</v>
       </c>
       <c r="F182" t="s">
-        <v>175</v>
+        <v>261</v>
       </c>
       <c r="G182" s="1">
         <v>13.16</v>
       </c>
       <c r="H182" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>174</v>
+        <v>259</v>
       </c>
       <c r="B183" t="s">
-        <v>174</v>
+        <v>260</v>
       </c>
       <c r="C183" s="1">
         <v>14.95</v>
@@ -6163,21 +6703,21 @@
         <v>1.79</v>
       </c>
       <c r="F183" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="G183" s="1">
         <v>13.19</v>
       </c>
       <c r="H183" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>174</v>
+        <v>259</v>
       </c>
       <c r="B184" t="s">
-        <v>174</v>
+        <v>260</v>
       </c>
       <c r="C184" s="1">
         <v>14.95</v>
@@ -6189,21 +6729,21 @@
         <v>1.79</v>
       </c>
       <c r="F184" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G184" s="1">
         <v>14.2</v>
       </c>
       <c r="H184" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>176</v>
+        <v>262</v>
       </c>
       <c r="B185" t="s">
-        <v>176</v>
+        <v>263</v>
       </c>
       <c r="C185" s="1">
         <v>17.75</v>
@@ -6215,21 +6755,21 @@
         <v>1.76</v>
       </c>
       <c r="F185" t="s">
-        <v>173</v>
+        <v>258</v>
       </c>
       <c r="G185" s="1">
         <v>15.99</v>
       </c>
       <c r="H185" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>177</v>
+        <v>264</v>
       </c>
       <c r="B186" t="s">
-        <v>177</v>
+        <v>265</v>
       </c>
       <c r="C186" s="1">
         <v>15.95</v>
@@ -6241,21 +6781,21 @@
         <v>1.75</v>
       </c>
       <c r="F186" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G186" s="1">
         <v>14.2</v>
       </c>
       <c r="H186" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>178</v>
+        <v>266</v>
       </c>
       <c r="B187" t="s">
-        <v>178</v>
+        <v>267</v>
       </c>
       <c r="C187" s="1">
         <v>14.45</v>
@@ -6267,21 +6807,21 @@
         <v>1.67</v>
       </c>
       <c r="F187" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G187" s="1">
         <v>12.78</v>
       </c>
       <c r="H187" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>179</v>
+        <v>268</v>
       </c>
       <c r="B188" t="s">
-        <v>179</v>
+        <v>269</v>
       </c>
       <c r="C188" s="1">
         <v>14.95</v>
@@ -6293,21 +6833,21 @@
         <v>1.62</v>
       </c>
       <c r="F188" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G188" s="1">
         <v>13.33</v>
       </c>
       <c r="H188" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="B189" t="s">
-        <v>180</v>
+        <v>271</v>
       </c>
       <c r="C189" s="1">
         <v>15.95</v>
@@ -6319,21 +6859,21 @@
         <v>1.61</v>
       </c>
       <c r="F189" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G189" s="1">
         <v>14.34</v>
       </c>
       <c r="H189" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>181</v>
+        <v>272</v>
       </c>
       <c r="B190" t="s">
-        <v>181</v>
+        <v>272</v>
       </c>
       <c r="C190" s="1">
         <v>10.45</v>
@@ -6345,21 +6885,21 @@
         <v>1.55</v>
       </c>
       <c r="F190" t="s">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="G190" s="1">
         <v>8.9</v>
       </c>
       <c r="H190" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>182</v>
+        <v>273</v>
       </c>
       <c r="B191" t="s">
-        <v>182</v>
+        <v>274</v>
       </c>
       <c r="C191" s="1">
         <v>10.49</v>
@@ -6371,21 +6911,21 @@
         <v>1.54</v>
       </c>
       <c r="F191" t="s">
-        <v>183</v>
+        <v>275</v>
       </c>
       <c r="G191" s="1">
         <v>8.95</v>
       </c>
       <c r="H191" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>184</v>
+        <v>276</v>
       </c>
       <c r="B192" t="s">
-        <v>184</v>
+        <v>277</v>
       </c>
       <c r="C192" s="1">
         <v>14.95</v>
@@ -6397,21 +6937,21 @@
         <v>1.52</v>
       </c>
       <c r="F192" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G192" s="1">
         <v>13.43</v>
       </c>
       <c r="H192" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>185</v>
+        <v>278</v>
       </c>
       <c r="B193" t="s">
-        <v>185</v>
+        <v>278</v>
       </c>
       <c r="C193" s="1">
         <v>14.95</v>
@@ -6423,21 +6963,21 @@
         <v>1.52</v>
       </c>
       <c r="F193" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G193" s="1">
         <v>13.43</v>
       </c>
       <c r="H193" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>186</v>
+        <v>279</v>
       </c>
       <c r="B194" t="s">
-        <v>186</v>
+        <v>279</v>
       </c>
       <c r="C194" s="1">
         <v>14.95</v>
@@ -6449,21 +6989,21 @@
         <v>1.52</v>
       </c>
       <c r="F194" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G194" s="1">
         <v>13.43</v>
       </c>
       <c r="H194" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>187</v>
+        <v>280</v>
       </c>
       <c r="B195" t="s">
-        <v>187</v>
+        <v>281</v>
       </c>
       <c r="C195" s="1">
         <v>10.45</v>
@@ -6475,21 +7015,21 @@
         <v>1.5</v>
       </c>
       <c r="F195" t="s">
-        <v>188</v>
+        <v>282</v>
       </c>
       <c r="G195" s="1">
         <v>8.95</v>
       </c>
       <c r="H195" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>189</v>
+        <v>283</v>
       </c>
       <c r="B196" t="s">
-        <v>189</v>
+        <v>284</v>
       </c>
       <c r="C196" s="1">
         <v>10.49</v>
@@ -6501,21 +7041,21 @@
         <v>1.5</v>
       </c>
       <c r="F196" t="s">
-        <v>190</v>
+        <v>285</v>
       </c>
       <c r="G196" s="1">
         <v>8.99</v>
       </c>
       <c r="H196" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>191</v>
+        <v>286</v>
       </c>
       <c r="B197" t="s">
-        <v>191</v>
+        <v>286</v>
       </c>
       <c r="C197" s="1">
         <v>9.49</v>
@@ -6527,21 +7067,21 @@
         <v>1.5</v>
       </c>
       <c r="F197" t="s">
-        <v>101</v>
+        <v>144</v>
       </c>
       <c r="G197" s="1">
         <v>7.99</v>
       </c>
       <c r="H197" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>192</v>
+        <v>287</v>
       </c>
       <c r="B198" t="s">
-        <v>192</v>
+        <v>287</v>
       </c>
       <c r="C198" s="1">
         <v>10.49</v>
@@ -6553,21 +7093,21 @@
         <v>1.5</v>
       </c>
       <c r="F198" t="s">
-        <v>101</v>
+        <v>144</v>
       </c>
       <c r="G198" s="1">
         <v>8.99</v>
       </c>
       <c r="H198" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>193</v>
+        <v>288</v>
       </c>
       <c r="B199" t="s">
-        <v>193</v>
+        <v>289</v>
       </c>
       <c r="C199" s="1">
         <v>12.95</v>
@@ -6579,21 +7119,21 @@
         <v>1.45</v>
       </c>
       <c r="F199" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G199" s="1">
         <v>11.5</v>
       </c>
       <c r="H199" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>194</v>
+        <v>290</v>
       </c>
       <c r="B200" t="s">
-        <v>194</v>
+        <v>291</v>
       </c>
       <c r="C200" s="1">
         <v>12.95</v>
@@ -6605,21 +7145,21 @@
         <v>1.45</v>
       </c>
       <c r="F200" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G200" s="1">
         <v>11.5</v>
       </c>
       <c r="H200" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>195</v>
+        <v>292</v>
       </c>
       <c r="B201" t="s">
-        <v>195</v>
+        <v>293</v>
       </c>
       <c r="C201" s="1">
         <v>12.95</v>
@@ -6631,21 +7171,21 @@
         <v>1.45</v>
       </c>
       <c r="F201" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G201" s="1">
         <v>11.5</v>
       </c>
       <c r="H201" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>196</v>
+        <v>294</v>
       </c>
       <c r="B202" t="s">
-        <v>196</v>
+        <v>295</v>
       </c>
       <c r="C202" s="1">
         <v>12.95</v>
@@ -6657,21 +7197,21 @@
         <v>1.45</v>
       </c>
       <c r="F202" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G202" s="1">
         <v>11.5</v>
       </c>
       <c r="H202" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>197</v>
+        <v>296</v>
       </c>
       <c r="B203" t="s">
-        <v>197</v>
+        <v>297</v>
       </c>
       <c r="C203" s="1">
         <v>12.95</v>
@@ -6683,21 +7223,21 @@
         <v>1.45</v>
       </c>
       <c r="F203" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G203" s="1">
         <v>11.5</v>
       </c>
       <c r="H203" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>198</v>
+        <v>298</v>
       </c>
       <c r="B204" t="s">
-        <v>198</v>
+        <v>299</v>
       </c>
       <c r="C204" s="1">
         <v>12.95</v>
@@ -6709,21 +7249,21 @@
         <v>1.45</v>
       </c>
       <c r="F204" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G204" s="1">
         <v>11.5</v>
       </c>
       <c r="H204" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>199</v>
+        <v>300</v>
       </c>
       <c r="B205" t="s">
-        <v>199</v>
+        <v>301</v>
       </c>
       <c r="C205" s="1">
         <v>12.95</v>
@@ -6735,21 +7275,21 @@
         <v>1.45</v>
       </c>
       <c r="F205" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G205" s="1">
         <v>11.5</v>
       </c>
       <c r="H205" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>200</v>
+        <v>302</v>
       </c>
       <c r="B206" t="s">
-        <v>200</v>
+        <v>303</v>
       </c>
       <c r="C206" s="1">
         <v>12.95</v>
@@ -6761,21 +7301,21 @@
         <v>1.45</v>
       </c>
       <c r="F206" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G206" s="1">
         <v>11.5</v>
       </c>
       <c r="H206" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>201</v>
+        <v>304</v>
       </c>
       <c r="B207" t="s">
-        <v>201</v>
+        <v>305</v>
       </c>
       <c r="C207" s="1">
         <v>12.95</v>
@@ -6787,21 +7327,21 @@
         <v>1.45</v>
       </c>
       <c r="F207" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G207" s="1">
         <v>11.5</v>
       </c>
       <c r="H207" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>202</v>
+        <v>306</v>
       </c>
       <c r="B208" t="s">
-        <v>202</v>
+        <v>307</v>
       </c>
       <c r="C208" s="1">
         <v>12.95</v>
@@ -6813,21 +7353,21 @@
         <v>1.45</v>
       </c>
       <c r="F208" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G208" s="1">
         <v>11.5</v>
       </c>
       <c r="H208" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>203</v>
+        <v>308</v>
       </c>
       <c r="B209" t="s">
-        <v>203</v>
+        <v>309</v>
       </c>
       <c r="C209" s="1">
         <v>12.95</v>
@@ -6839,21 +7379,21 @@
         <v>1.45</v>
       </c>
       <c r="F209" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G209" s="1">
         <v>11.5</v>
       </c>
       <c r="H209" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
       <c r="B210" t="s">
-        <v>204</v>
+        <v>311</v>
       </c>
       <c r="C210" s="1">
         <v>12.95</v>
@@ -6865,21 +7405,21 @@
         <v>1.45</v>
       </c>
       <c r="F210" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G210" s="1">
         <v>11.5</v>
       </c>
       <c r="H210" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>205</v>
+        <v>312</v>
       </c>
       <c r="B211" t="s">
-        <v>205</v>
+        <v>313</v>
       </c>
       <c r="C211" s="1">
         <v>12.95</v>
@@ -6891,21 +7431,21 @@
         <v>1.45</v>
       </c>
       <c r="F211" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G211" s="1">
         <v>11.5</v>
       </c>
       <c r="H211" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>206</v>
+        <v>314</v>
       </c>
       <c r="B212" t="s">
-        <v>206</v>
+        <v>315</v>
       </c>
       <c r="C212" s="1">
         <v>12.95</v>
@@ -6917,21 +7457,21 @@
         <v>1.45</v>
       </c>
       <c r="F212" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G212" s="1">
         <v>11.5</v>
       </c>
       <c r="H212" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>207</v>
+        <v>316</v>
       </c>
       <c r="B213" t="s">
-        <v>207</v>
+        <v>317</v>
       </c>
       <c r="C213" s="1">
         <v>12.95</v>
@@ -6943,21 +7483,21 @@
         <v>1.45</v>
       </c>
       <c r="F213" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G213" s="1">
         <v>11.5</v>
       </c>
       <c r="H213" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>208</v>
+        <v>318</v>
       </c>
       <c r="B214" t="s">
-        <v>208</v>
+        <v>319</v>
       </c>
       <c r="C214" s="1">
         <v>12.95</v>
@@ -6969,21 +7509,21 @@
         <v>1.45</v>
       </c>
       <c r="F214" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G214" s="1">
         <v>11.5</v>
       </c>
       <c r="H214" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>209</v>
+        <v>320</v>
       </c>
       <c r="B215" t="s">
-        <v>209</v>
+        <v>321</v>
       </c>
       <c r="C215" s="1">
         <v>12.95</v>
@@ -6995,21 +7535,21 @@
         <v>1.45</v>
       </c>
       <c r="F215" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G215" s="1">
         <v>11.5</v>
       </c>
       <c r="H215" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>210</v>
+        <v>322</v>
       </c>
       <c r="B216" t="s">
-        <v>210</v>
+        <v>322</v>
       </c>
       <c r="C216" s="1">
         <v>12.95</v>
@@ -7021,21 +7561,21 @@
         <v>1.45</v>
       </c>
       <c r="F216" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G216" s="1">
         <v>11.5</v>
       </c>
       <c r="H216" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>211</v>
+        <v>323</v>
       </c>
       <c r="B217" t="s">
-        <v>211</v>
+        <v>323</v>
       </c>
       <c r="C217" s="1">
         <v>12.95</v>
@@ -7047,21 +7587,21 @@
         <v>1.45</v>
       </c>
       <c r="F217" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G217" s="1">
         <v>11.5</v>
       </c>
       <c r="H217" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>212</v>
+        <v>324</v>
       </c>
       <c r="B218" t="s">
-        <v>212</v>
+        <v>324</v>
       </c>
       <c r="C218" s="1">
         <v>12.95</v>
@@ -7073,21 +7613,21 @@
         <v>1.45</v>
       </c>
       <c r="F218" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G218" s="1">
         <v>11.5</v>
       </c>
       <c r="H218" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>213</v>
+        <v>325</v>
       </c>
       <c r="B219" t="s">
-        <v>213</v>
+        <v>325</v>
       </c>
       <c r="C219" s="1">
         <v>12.95</v>
@@ -7099,21 +7639,21 @@
         <v>1.45</v>
       </c>
       <c r="F219" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G219" s="1">
         <v>11.5</v>
       </c>
       <c r="H219" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>214</v>
+        <v>326</v>
       </c>
       <c r="B220" t="s">
-        <v>214</v>
+        <v>326</v>
       </c>
       <c r="C220" s="1">
         <v>14.95</v>
@@ -7125,21 +7665,21 @@
         <v>1.42</v>
       </c>
       <c r="F220" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G220" s="1">
         <v>13.53</v>
       </c>
       <c r="H220" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>215</v>
+        <v>327</v>
       </c>
       <c r="B221" t="s">
-        <v>215</v>
+        <v>327</v>
       </c>
       <c r="C221" s="1">
         <v>14.95</v>
@@ -7151,21 +7691,21 @@
         <v>1.42</v>
       </c>
       <c r="F221" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G221" s="1">
         <v>13.53</v>
       </c>
       <c r="H221" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>216</v>
+        <v>328</v>
       </c>
       <c r="B222" t="s">
-        <v>216</v>
+        <v>329</v>
       </c>
       <c r="C222" s="1">
         <v>11.9</v>
@@ -7177,21 +7717,21 @@
         <v>1.4</v>
       </c>
       <c r="F222" t="s">
-        <v>217</v>
+        <v>330</v>
       </c>
       <c r="G222" s="1">
         <v>10.5</v>
       </c>
       <c r="H222" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>218</v>
+        <v>331</v>
       </c>
       <c r="B223" t="s">
-        <v>218</v>
+        <v>331</v>
       </c>
       <c r="C223" s="1">
         <v>15.4</v>
@@ -7203,21 +7743,21 @@
         <v>1.4</v>
       </c>
       <c r="F223" t="s">
-        <v>217</v>
+        <v>330</v>
       </c>
       <c r="G223" s="1">
         <v>14</v>
       </c>
       <c r="H223" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>218</v>
+        <v>331</v>
       </c>
       <c r="B224" t="s">
-        <v>218</v>
+        <v>331</v>
       </c>
       <c r="C224" s="1">
         <v>15.4</v>
@@ -7229,21 +7769,21 @@
         <v>1.4</v>
       </c>
       <c r="F224" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G224" s="1">
         <v>14.75</v>
       </c>
       <c r="H224" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>219</v>
+        <v>332</v>
       </c>
       <c r="B225" t="s">
-        <v>219</v>
+        <v>333</v>
       </c>
       <c r="C225" s="1">
         <v>11.19</v>
@@ -7255,21 +7795,21 @@
         <v>1.39</v>
       </c>
       <c r="F225" t="s">
-        <v>217</v>
+        <v>330</v>
       </c>
       <c r="G225" s="1">
         <v>9.8</v>
       </c>
       <c r="H225" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>220</v>
+        <v>334</v>
       </c>
       <c r="B226" t="s">
-        <v>220</v>
+        <v>335</v>
       </c>
       <c r="C226" s="1">
         <v>13.49</v>
@@ -7281,21 +7821,21 @@
         <v>1.3</v>
       </c>
       <c r="F226" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="G226" s="1">
         <v>12.19</v>
       </c>
       <c r="H226" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>221</v>
+        <v>336</v>
       </c>
       <c r="B227" t="s">
-        <v>221</v>
+        <v>337</v>
       </c>
       <c r="C227" s="1">
         <v>12.75</v>
@@ -7307,21 +7847,21 @@
         <v>1.25</v>
       </c>
       <c r="F227" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G227" s="1">
         <v>11.5</v>
       </c>
       <c r="H227" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>222</v>
+        <v>338</v>
       </c>
       <c r="B228" t="s">
-        <v>222</v>
+        <v>339</v>
       </c>
       <c r="C228" s="1">
         <v>14.95</v>
@@ -7333,21 +7873,21 @@
         <v>1.2</v>
       </c>
       <c r="F228" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G228" s="1">
         <v>13.75</v>
       </c>
       <c r="H228" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>223</v>
+        <v>340</v>
       </c>
       <c r="B229" t="s">
-        <v>223</v>
+        <v>341</v>
       </c>
       <c r="C229" s="1">
         <v>12.69</v>
@@ -7359,21 +7899,21 @@
         <v>1.19</v>
       </c>
       <c r="F229" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G229" s="1">
         <v>11.5</v>
       </c>
       <c r="H229" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>224</v>
+        <v>342</v>
       </c>
       <c r="B230" t="s">
-        <v>224</v>
+        <v>343</v>
       </c>
       <c r="C230" s="1">
         <v>15.95</v>
@@ -7385,21 +7925,21 @@
         <v>1.17</v>
       </c>
       <c r="F230" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G230" s="1">
         <v>14.78</v>
       </c>
       <c r="H230" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>225</v>
+        <v>344</v>
       </c>
       <c r="B231" t="s">
-        <v>225</v>
+        <v>345</v>
       </c>
       <c r="C231" s="1">
         <v>15.95</v>
@@ -7411,21 +7951,21 @@
         <v>1.17</v>
       </c>
       <c r="F231" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G231" s="1">
         <v>14.78</v>
       </c>
       <c r="H231" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>226</v>
+        <v>346</v>
       </c>
       <c r="B232" t="s">
-        <v>226</v>
+        <v>347</v>
       </c>
       <c r="C232" s="1">
         <v>15.95</v>
@@ -7437,21 +7977,21 @@
         <v>1.17</v>
       </c>
       <c r="F232" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G232" s="1">
         <v>14.78</v>
       </c>
       <c r="H232" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>227</v>
+        <v>348</v>
       </c>
       <c r="B233" t="s">
-        <v>227</v>
+        <v>349</v>
       </c>
       <c r="C233" s="1">
         <v>15.95</v>
@@ -7463,21 +8003,21 @@
         <v>1.17</v>
       </c>
       <c r="F233" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G233" s="1">
         <v>14.78</v>
       </c>
       <c r="H233" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>228</v>
+        <v>350</v>
       </c>
       <c r="B234" t="s">
-        <v>228</v>
+        <v>351</v>
       </c>
       <c r="C234" s="1">
         <v>10.45</v>
@@ -7489,21 +8029,21 @@
         <v>1.16</v>
       </c>
       <c r="F234" t="s">
-        <v>101</v>
+        <v>144</v>
       </c>
       <c r="G234" s="1">
         <v>9.29</v>
       </c>
       <c r="H234" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>229</v>
+        <v>352</v>
       </c>
       <c r="B235" t="s">
-        <v>229</v>
+        <v>352</v>
       </c>
       <c r="C235" s="1">
         <v>14.95</v>
@@ -7515,21 +8055,21 @@
         <v>1.13</v>
       </c>
       <c r="F235" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G235" s="1">
         <v>13.82</v>
       </c>
       <c r="H235" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>230</v>
+        <v>353</v>
       </c>
       <c r="B236" t="s">
-        <v>230</v>
+        <v>353</v>
       </c>
       <c r="C236" s="1">
         <v>12.59</v>
@@ -7541,21 +8081,21 @@
         <v>1.09</v>
       </c>
       <c r="F236" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G236" s="1">
         <v>11.5</v>
       </c>
       <c r="H236" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>231</v>
+        <v>354</v>
       </c>
       <c r="B237" t="s">
-        <v>231</v>
+        <v>355</v>
       </c>
       <c r="C237" s="1">
         <v>15.95</v>
@@ -7567,21 +8107,21 @@
         <v>1.06</v>
       </c>
       <c r="F237" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="G237" s="1">
         <v>14.89</v>
       </c>
       <c r="H237" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>232</v>
+        <v>356</v>
       </c>
       <c r="B238" t="s">
-        <v>232</v>
+        <v>357</v>
       </c>
       <c r="C238" s="1">
         <v>15.95</v>
@@ -7593,21 +8133,21 @@
         <v>1.06</v>
       </c>
       <c r="F238" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="G238" s="1">
         <v>14.89</v>
       </c>
       <c r="H238" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>233</v>
+        <v>358</v>
       </c>
       <c r="B239" t="s">
-        <v>233</v>
+        <v>359</v>
       </c>
       <c r="C239" s="1">
         <v>15.95</v>
@@ -7619,21 +8159,21 @@
         <v>1</v>
       </c>
       <c r="F239" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G239" s="1">
         <v>14.95</v>
       </c>
       <c r="H239" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>234</v>
+        <v>360</v>
       </c>
       <c r="B240" t="s">
-        <v>234</v>
+        <v>361</v>
       </c>
       <c r="C240" s="1">
         <v>15.95</v>
@@ -7645,21 +8185,21 @@
         <v>1</v>
       </c>
       <c r="F240" t="s">
-        <v>235</v>
+        <v>362</v>
       </c>
       <c r="G240" s="1">
         <v>14.95</v>
       </c>
       <c r="H240" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>236</v>
+        <v>363</v>
       </c>
       <c r="B241" t="s">
-        <v>236</v>
+        <v>363</v>
       </c>
       <c r="C241" s="1">
         <v>10.99</v>
@@ -7671,21 +8211,21 @@
         <v>1</v>
       </c>
       <c r="F241" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G241" s="1">
         <v>9.99</v>
       </c>
       <c r="H241" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>237</v>
+        <v>364</v>
       </c>
       <c r="B242" t="s">
-        <v>237</v>
+        <v>364</v>
       </c>
       <c r="C242" s="1">
         <v>9.99</v>
@@ -7697,21 +8237,21 @@
         <v>0.99</v>
       </c>
       <c r="F242" t="s">
-        <v>238</v>
+        <v>365</v>
       </c>
       <c r="G242" s="1">
         <v>9</v>
       </c>
       <c r="H242" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>239</v>
+        <v>366</v>
       </c>
       <c r="B243" t="s">
-        <v>239</v>
+        <v>367</v>
       </c>
       <c r="C243" s="1">
         <v>14.95</v>
@@ -7723,21 +8263,21 @@
         <v>0.98</v>
       </c>
       <c r="F243" t="s">
-        <v>217</v>
+        <v>330</v>
       </c>
       <c r="G243" s="1">
         <v>13.97</v>
       </c>
       <c r="H243" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>240</v>
+        <v>368</v>
       </c>
       <c r="B244" t="s">
-        <v>240</v>
+        <v>369</v>
       </c>
       <c r="C244" s="1">
         <v>15.69</v>
@@ -7749,21 +8289,21 @@
         <v>0.91</v>
       </c>
       <c r="F244" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G244" s="1">
         <v>14.78</v>
       </c>
       <c r="H244" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>241</v>
+        <v>370</v>
       </c>
       <c r="B245" t="s">
-        <v>241</v>
+        <v>371</v>
       </c>
       <c r="C245" s="1">
         <v>14.95</v>
@@ -7775,21 +8315,21 @@
         <v>0.88</v>
       </c>
       <c r="F245" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G245" s="1">
         <v>14.07</v>
       </c>
       <c r="H245" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>242</v>
+        <v>372</v>
       </c>
       <c r="B246" t="s">
-        <v>242</v>
+        <v>373</v>
       </c>
       <c r="C246" s="1">
         <v>12</v>
@@ -7801,21 +8341,21 @@
         <v>0.8</v>
       </c>
       <c r="F246" t="s">
-        <v>217</v>
+        <v>330</v>
       </c>
       <c r="G246" s="1">
         <v>11.2</v>
       </c>
       <c r="H246" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>243</v>
+        <v>374</v>
       </c>
       <c r="B247" t="s">
-        <v>243</v>
+        <v>375</v>
       </c>
       <c r="C247" s="1">
         <v>9.49</v>
@@ -7827,21 +8367,21 @@
         <v>0.8</v>
       </c>
       <c r="F247" t="s">
-        <v>155</v>
+        <v>227</v>
       </c>
       <c r="G247" s="1">
         <v>8.69</v>
       </c>
       <c r="H247" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>244</v>
+        <v>376</v>
       </c>
       <c r="B248" t="s">
-        <v>244</v>
+        <v>376</v>
       </c>
       <c r="C248" s="1">
         <v>9.49</v>
@@ -7853,21 +8393,21 @@
         <v>0.8</v>
       </c>
       <c r="F248" t="s">
-        <v>155</v>
+        <v>227</v>
       </c>
       <c r="G248" s="1">
         <v>8.69</v>
       </c>
       <c r="H248" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>245</v>
+        <v>377</v>
       </c>
       <c r="B249" t="s">
-        <v>245</v>
+        <v>377</v>
       </c>
       <c r="C249" s="1">
         <v>14.95</v>
@@ -7879,21 +8419,21 @@
         <v>0.78</v>
       </c>
       <c r="F249" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G249" s="1">
         <v>14.17</v>
       </c>
       <c r="H249" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>246</v>
+        <v>378</v>
       </c>
       <c r="B250" t="s">
-        <v>246</v>
+        <v>379</v>
       </c>
       <c r="C250" s="1">
         <v>14.95</v>
@@ -7905,21 +8445,21 @@
         <v>0.75</v>
       </c>
       <c r="F250" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G250" s="1">
         <v>14.2</v>
       </c>
       <c r="H250" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>247</v>
+        <v>380</v>
       </c>
       <c r="B251" t="s">
-        <v>247</v>
+        <v>381</v>
       </c>
       <c r="C251" s="1">
         <v>14.95</v>
@@ -7931,21 +8471,21 @@
         <v>0.75</v>
       </c>
       <c r="F251" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G251" s="1">
         <v>14.2</v>
       </c>
       <c r="H251" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>248</v>
+        <v>382</v>
       </c>
       <c r="B252" t="s">
-        <v>248</v>
+        <v>383</v>
       </c>
       <c r="C252" s="1">
         <v>14.95</v>
@@ -7957,21 +8497,21 @@
         <v>0.75</v>
       </c>
       <c r="F252" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G252" s="1">
         <v>14.2</v>
       </c>
       <c r="H252" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>249</v>
+        <v>384</v>
       </c>
       <c r="B253" t="s">
-        <v>249</v>
+        <v>385</v>
       </c>
       <c r="C253" s="1">
         <v>14.95</v>
@@ -7983,21 +8523,21 @@
         <v>0.75</v>
       </c>
       <c r="F253" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G253" s="1">
         <v>14.2</v>
       </c>
       <c r="H253" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>250</v>
+        <v>386</v>
       </c>
       <c r="B254" t="s">
-        <v>250</v>
+        <v>387</v>
       </c>
       <c r="C254" s="1">
         <v>14.95</v>
@@ -8009,21 +8549,21 @@
         <v>0.75</v>
       </c>
       <c r="F254" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G254" s="1">
         <v>14.2</v>
       </c>
       <c r="H254" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>251</v>
+        <v>388</v>
       </c>
       <c r="B255" t="s">
-        <v>251</v>
+        <v>389</v>
       </c>
       <c r="C255" s="1">
         <v>14.95</v>
@@ -8035,21 +8575,21 @@
         <v>0.75</v>
       </c>
       <c r="F255" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G255" s="1">
         <v>14.2</v>
       </c>
       <c r="H255" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>252</v>
+        <v>390</v>
       </c>
       <c r="B256" t="s">
-        <v>252</v>
+        <v>391</v>
       </c>
       <c r="C256" s="1">
         <v>14.95</v>
@@ -8061,21 +8601,21 @@
         <v>0.75</v>
       </c>
       <c r="F256" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G256" s="1">
         <v>14.2</v>
       </c>
       <c r="H256" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>253</v>
+        <v>392</v>
       </c>
       <c r="B257" t="s">
-        <v>253</v>
+        <v>393</v>
       </c>
       <c r="C257" s="1">
         <v>14.95</v>
@@ -8087,21 +8627,21 @@
         <v>0.75</v>
       </c>
       <c r="F257" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G257" s="1">
         <v>14.2</v>
       </c>
       <c r="H257" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>254</v>
+        <v>394</v>
       </c>
       <c r="B258" t="s">
-        <v>254</v>
+        <v>395</v>
       </c>
       <c r="C258" s="1">
         <v>14.95</v>
@@ -8113,21 +8653,21 @@
         <v>0.75</v>
       </c>
       <c r="F258" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G258" s="1">
         <v>14.2</v>
       </c>
       <c r="H258" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>255</v>
+        <v>396</v>
       </c>
       <c r="B259" t="s">
-        <v>255</v>
+        <v>397</v>
       </c>
       <c r="C259" s="1">
         <v>14.95</v>
@@ -8139,21 +8679,21 @@
         <v>0.75</v>
       </c>
       <c r="F259" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G259" s="1">
         <v>14.2</v>
       </c>
       <c r="H259" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>256</v>
+        <v>398</v>
       </c>
       <c r="B260" t="s">
-        <v>256</v>
+        <v>399</v>
       </c>
       <c r="C260" s="1">
         <v>14.95</v>
@@ -8165,21 +8705,21 @@
         <v>0.75</v>
       </c>
       <c r="F260" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G260" s="1">
         <v>14.2</v>
       </c>
       <c r="H260" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>257</v>
+        <v>400</v>
       </c>
       <c r="B261" t="s">
-        <v>257</v>
+        <v>401</v>
       </c>
       <c r="C261" s="1">
         <v>14.95</v>
@@ -8191,21 +8731,21 @@
         <v>0.75</v>
       </c>
       <c r="F261" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G261" s="1">
         <v>14.2</v>
       </c>
       <c r="H261" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>258</v>
+        <v>402</v>
       </c>
       <c r="B262" t="s">
-        <v>258</v>
+        <v>403</v>
       </c>
       <c r="C262" s="1">
         <v>14.95</v>
@@ -8217,21 +8757,21 @@
         <v>0.75</v>
       </c>
       <c r="F262" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G262" s="1">
         <v>14.2</v>
       </c>
       <c r="H262" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>259</v>
+        <v>404</v>
       </c>
       <c r="B263" t="s">
-        <v>259</v>
+        <v>405</v>
       </c>
       <c r="C263" s="1">
         <v>14.95</v>
@@ -8243,21 +8783,21 @@
         <v>0.75</v>
       </c>
       <c r="F263" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G263" s="1">
         <v>14.2</v>
       </c>
       <c r="H263" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>260</v>
+        <v>406</v>
       </c>
       <c r="B264" t="s">
-        <v>260</v>
+        <v>407</v>
       </c>
       <c r="C264" s="1">
         <v>14.95</v>
@@ -8269,21 +8809,21 @@
         <v>0.75</v>
       </c>
       <c r="F264" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G264" s="1">
         <v>14.2</v>
       </c>
       <c r="H264" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>261</v>
+        <v>408</v>
       </c>
       <c r="B265" t="s">
-        <v>261</v>
+        <v>409</v>
       </c>
       <c r="C265" s="1">
         <v>14.95</v>
@@ -8295,21 +8835,21 @@
         <v>0.75</v>
       </c>
       <c r="F265" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G265" s="1">
         <v>14.2</v>
       </c>
       <c r="H265" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>262</v>
+        <v>410</v>
       </c>
       <c r="B266" t="s">
-        <v>262</v>
+        <v>411</v>
       </c>
       <c r="C266" s="1">
         <v>14.95</v>
@@ -8321,21 +8861,21 @@
         <v>0.75</v>
       </c>
       <c r="F266" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G266" s="1">
         <v>14.2</v>
       </c>
       <c r="H266" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>263</v>
+        <v>412</v>
       </c>
       <c r="B267" t="s">
-        <v>263</v>
+        <v>413</v>
       </c>
       <c r="C267" s="1">
         <v>14.95</v>
@@ -8347,21 +8887,21 @@
         <v>0.75</v>
       </c>
       <c r="F267" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G267" s="1">
         <v>14.2</v>
       </c>
       <c r="H267" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>264</v>
+        <v>414</v>
       </c>
       <c r="B268" t="s">
-        <v>264</v>
+        <v>415</v>
       </c>
       <c r="C268" s="1">
         <v>14.95</v>
@@ -8373,21 +8913,21 @@
         <v>0.75</v>
       </c>
       <c r="F268" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G268" s="1">
         <v>14.2</v>
       </c>
       <c r="H268" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>265</v>
+        <v>416</v>
       </c>
       <c r="B269" t="s">
-        <v>265</v>
+        <v>417</v>
       </c>
       <c r="C269" s="1">
         <v>14.95</v>
@@ -8399,21 +8939,21 @@
         <v>0.75</v>
       </c>
       <c r="F269" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G269" s="1">
         <v>14.2</v>
       </c>
       <c r="H269" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>266</v>
+        <v>418</v>
       </c>
       <c r="B270" t="s">
-        <v>266</v>
+        <v>419</v>
       </c>
       <c r="C270" s="1">
         <v>14.95</v>
@@ -8425,21 +8965,21 @@
         <v>0.75</v>
       </c>
       <c r="F270" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G270" s="1">
         <v>14.2</v>
       </c>
       <c r="H270" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>267</v>
+        <v>420</v>
       </c>
       <c r="B271" t="s">
-        <v>267</v>
+        <v>421</v>
       </c>
       <c r="C271" s="1">
         <v>14.95</v>
@@ -8451,21 +8991,21 @@
         <v>0.75</v>
       </c>
       <c r="F271" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G271" s="1">
         <v>14.2</v>
       </c>
       <c r="H271" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>268</v>
+        <v>422</v>
       </c>
       <c r="B272" t="s">
-        <v>268</v>
+        <v>423</v>
       </c>
       <c r="C272" s="1">
         <v>14.95</v>
@@ -8477,21 +9017,21 @@
         <v>0.75</v>
       </c>
       <c r="F272" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G272" s="1">
         <v>14.2</v>
       </c>
       <c r="H272" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>269</v>
+        <v>424</v>
       </c>
       <c r="B273" t="s">
-        <v>269</v>
+        <v>425</v>
       </c>
       <c r="C273" s="1">
         <v>14.95</v>
@@ -8503,21 +9043,21 @@
         <v>0.75</v>
       </c>
       <c r="F273" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G273" s="1">
         <v>14.2</v>
       </c>
       <c r="H273" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>270</v>
+        <v>426</v>
       </c>
       <c r="B274" t="s">
-        <v>270</v>
+        <v>426</v>
       </c>
       <c r="C274" s="1">
         <v>14.95</v>
@@ -8529,21 +9069,21 @@
         <v>0.75</v>
       </c>
       <c r="F274" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G274" s="1">
         <v>14.2</v>
       </c>
       <c r="H274" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>271</v>
+        <v>427</v>
       </c>
       <c r="B275" t="s">
-        <v>271</v>
+        <v>427</v>
       </c>
       <c r="C275" s="1">
         <v>14.95</v>
@@ -8555,21 +9095,21 @@
         <v>0.75</v>
       </c>
       <c r="F275" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G275" s="1">
         <v>14.2</v>
       </c>
       <c r="H275" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>272</v>
+        <v>428</v>
       </c>
       <c r="B276" t="s">
-        <v>272</v>
+        <v>428</v>
       </c>
       <c r="C276" s="1">
         <v>14.95</v>
@@ -8581,21 +9121,21 @@
         <v>0.75</v>
       </c>
       <c r="F276" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G276" s="1">
         <v>14.2</v>
       </c>
       <c r="H276" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>273</v>
+        <v>429</v>
       </c>
       <c r="B277" t="s">
-        <v>273</v>
+        <v>429</v>
       </c>
       <c r="C277" s="1">
         <v>14.95</v>
@@ -8607,21 +9147,21 @@
         <v>0.75</v>
       </c>
       <c r="F277" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G277" s="1">
         <v>14.2</v>
       </c>
       <c r="H277" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>274</v>
+        <v>430</v>
       </c>
       <c r="B278" t="s">
-        <v>274</v>
+        <v>430</v>
       </c>
       <c r="C278" s="1">
         <v>14.95</v>
@@ -8633,21 +9173,21 @@
         <v>0.75</v>
       </c>
       <c r="F278" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G278" s="1">
         <v>14.2</v>
       </c>
       <c r="H278" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>275</v>
+        <v>431</v>
       </c>
       <c r="B279" t="s">
-        <v>275</v>
+        <v>431</v>
       </c>
       <c r="C279" s="1">
         <v>14.95</v>
@@ -8659,21 +9199,21 @@
         <v>0.75</v>
       </c>
       <c r="F279" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G279" s="1">
         <v>14.2</v>
       </c>
       <c r="H279" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>276</v>
+        <v>432</v>
       </c>
       <c r="B280" t="s">
-        <v>276</v>
+        <v>432</v>
       </c>
       <c r="C280" s="1">
         <v>14.95</v>
@@ -8685,21 +9225,21 @@
         <v>0.75</v>
       </c>
       <c r="F280" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G280" s="1">
         <v>14.2</v>
       </c>
       <c r="H280" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>277</v>
+        <v>433</v>
       </c>
       <c r="B281" t="s">
-        <v>277</v>
+        <v>433</v>
       </c>
       <c r="C281" s="1">
         <v>14.95</v>
@@ -8711,21 +9251,21 @@
         <v>0.75</v>
       </c>
       <c r="F281" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G281" s="1">
         <v>14.2</v>
       </c>
       <c r="H281" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>278</v>
+        <v>434</v>
       </c>
       <c r="B282" t="s">
-        <v>278</v>
+        <v>434</v>
       </c>
       <c r="C282" s="1">
         <v>14.95</v>
@@ -8737,21 +9277,21 @@
         <v>0.75</v>
       </c>
       <c r="F282" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G282" s="1">
         <v>14.2</v>
       </c>
       <c r="H282" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>279</v>
+        <v>435</v>
       </c>
       <c r="B283" t="s">
-        <v>279</v>
+        <v>435</v>
       </c>
       <c r="C283" s="1">
         <v>14.95</v>
@@ -8763,21 +9303,21 @@
         <v>0.75</v>
       </c>
       <c r="F283" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G283" s="1">
         <v>14.2</v>
       </c>
       <c r="H283" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>280</v>
+        <v>436</v>
       </c>
       <c r="B284" t="s">
-        <v>280</v>
+        <v>436</v>
       </c>
       <c r="C284" s="1">
         <v>14.95</v>
@@ -8789,21 +9329,21 @@
         <v>0.75</v>
       </c>
       <c r="F284" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G284" s="1">
         <v>14.2</v>
       </c>
       <c r="H284" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>281</v>
+        <v>437</v>
       </c>
       <c r="B285" t="s">
-        <v>281</v>
+        <v>437</v>
       </c>
       <c r="C285" s="1">
         <v>14.95</v>
@@ -8815,21 +9355,21 @@
         <v>0.75</v>
       </c>
       <c r="F285" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G285" s="1">
         <v>14.2</v>
       </c>
       <c r="H285" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>282</v>
+        <v>438</v>
       </c>
       <c r="B286" t="s">
-        <v>282</v>
+        <v>438</v>
       </c>
       <c r="C286" s="1">
         <v>14.95</v>
@@ -8841,21 +9381,21 @@
         <v>0.75</v>
       </c>
       <c r="F286" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G286" s="1">
         <v>14.2</v>
       </c>
       <c r="H286" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>283</v>
+        <v>439</v>
       </c>
       <c r="B287" t="s">
-        <v>283</v>
+        <v>439</v>
       </c>
       <c r="C287" s="1">
         <v>14.95</v>
@@ -8867,21 +9407,21 @@
         <v>0.75</v>
       </c>
       <c r="F287" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G287" s="1">
         <v>14.2</v>
       </c>
       <c r="H287" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>284</v>
+        <v>440</v>
       </c>
       <c r="B288" t="s">
-        <v>284</v>
+        <v>440</v>
       </c>
       <c r="C288" s="1">
         <v>14.95</v>
@@ -8893,21 +9433,21 @@
         <v>0.75</v>
       </c>
       <c r="F288" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G288" s="1">
         <v>14.2</v>
       </c>
       <c r="H288" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>285</v>
+        <v>441</v>
       </c>
       <c r="B289" t="s">
-        <v>285</v>
+        <v>441</v>
       </c>
       <c r="C289" s="1">
         <v>14.95</v>
@@ -8919,21 +9459,21 @@
         <v>0.75</v>
       </c>
       <c r="F289" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G289" s="1">
         <v>14.2</v>
       </c>
       <c r="H289" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>286</v>
+        <v>442</v>
       </c>
       <c r="B290" t="s">
-        <v>286</v>
+        <v>443</v>
       </c>
       <c r="C290" s="1">
         <v>9.45</v>
@@ -8945,21 +9485,21 @@
         <v>0.66</v>
       </c>
       <c r="F290" t="s">
-        <v>101</v>
+        <v>144</v>
       </c>
       <c r="G290" s="1">
         <v>8.79</v>
       </c>
       <c r="H290" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>287</v>
+        <v>444</v>
       </c>
       <c r="B291" t="s">
-        <v>287</v>
+        <v>445</v>
       </c>
       <c r="C291" s="1">
         <v>14.95</v>
@@ -8971,21 +9511,21 @@
         <v>0.61</v>
       </c>
       <c r="F291" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G291" s="1">
         <v>14.34</v>
       </c>
       <c r="H291" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>288</v>
+        <v>446</v>
       </c>
       <c r="B292" t="s">
-        <v>288</v>
+        <v>447</v>
       </c>
       <c r="C292" s="1">
         <v>14.95</v>
@@ -8997,21 +9537,21 @@
         <v>0.61</v>
       </c>
       <c r="F292" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G292" s="1">
         <v>14.34</v>
       </c>
       <c r="H292" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>289</v>
+        <v>448</v>
       </c>
       <c r="B293" t="s">
-        <v>289</v>
+        <v>449</v>
       </c>
       <c r="C293" s="1">
         <v>14.95</v>
@@ -9023,21 +9563,21 @@
         <v>0.61</v>
       </c>
       <c r="F293" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G293" s="1">
         <v>14.34</v>
       </c>
       <c r="H293" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>290</v>
+        <v>450</v>
       </c>
       <c r="B294" t="s">
-        <v>290</v>
+        <v>451</v>
       </c>
       <c r="C294" s="1">
         <v>14.95</v>
@@ -9049,21 +9589,21 @@
         <v>0.61</v>
       </c>
       <c r="F294" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G294" s="1">
         <v>14.34</v>
       </c>
       <c r="H294" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>291</v>
+        <v>452</v>
       </c>
       <c r="B295" t="s">
-        <v>291</v>
+        <v>453</v>
       </c>
       <c r="C295" s="1">
         <v>14.95</v>
@@ -9075,21 +9615,21 @@
         <v>0.61</v>
       </c>
       <c r="F295" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G295" s="1">
         <v>14.34</v>
       </c>
       <c r="H295" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>292</v>
+        <v>454</v>
       </c>
       <c r="B296" t="s">
-        <v>292</v>
+        <v>454</v>
       </c>
       <c r="C296" s="1">
         <v>14.95</v>
@@ -9101,21 +9641,21 @@
         <v>0.61</v>
       </c>
       <c r="F296" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G296" s="1">
         <v>14.34</v>
       </c>
       <c r="H296" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>293</v>
+        <v>455</v>
       </c>
       <c r="B297" t="s">
-        <v>293</v>
+        <v>455</v>
       </c>
       <c r="C297" s="1">
         <v>14.95</v>
@@ -9127,21 +9667,21 @@
         <v>0.61</v>
       </c>
       <c r="F297" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G297" s="1">
         <v>14.34</v>
       </c>
       <c r="H297" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>294</v>
+        <v>456</v>
       </c>
       <c r="B298" t="s">
-        <v>294</v>
+        <v>456</v>
       </c>
       <c r="C298" s="1">
         <v>14.95</v>
@@ -9153,21 +9693,21 @@
         <v>0.61</v>
       </c>
       <c r="F298" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G298" s="1">
         <v>14.34</v>
       </c>
       <c r="H298" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>295</v>
+        <v>457</v>
       </c>
       <c r="B299" t="s">
-        <v>295</v>
+        <v>458</v>
       </c>
       <c r="C299" s="1">
         <v>14.75</v>
@@ -9179,21 +9719,21 @@
         <v>0.55</v>
       </c>
       <c r="F299" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G299" s="1">
         <v>14.2</v>
       </c>
       <c r="H299" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>296</v>
+        <v>459</v>
       </c>
       <c r="B300" t="s">
-        <v>296</v>
+        <v>460</v>
       </c>
       <c r="C300" s="1">
         <v>14.75</v>
@@ -9205,21 +9745,21 @@
         <v>0.55</v>
       </c>
       <c r="F300" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G300" s="1">
         <v>14.2</v>
       </c>
       <c r="H300" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>297</v>
+        <v>461</v>
       </c>
       <c r="B301" t="s">
-        <v>297</v>
+        <v>462</v>
       </c>
       <c r="C301" s="1">
         <v>14.75</v>
@@ -9231,21 +9771,21 @@
         <v>0.55</v>
       </c>
       <c r="F301" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G301" s="1">
         <v>14.2</v>
       </c>
       <c r="H301" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>298</v>
+        <v>463</v>
       </c>
       <c r="B302" t="s">
-        <v>298</v>
+        <v>463</v>
       </c>
       <c r="C302" s="1">
         <v>14.75</v>
@@ -9257,21 +9797,21 @@
         <v>0.55</v>
       </c>
       <c r="F302" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G302" s="1">
         <v>14.2</v>
       </c>
       <c r="H302" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>299</v>
+        <v>464</v>
       </c>
       <c r="B303" t="s">
-        <v>299</v>
+        <v>464</v>
       </c>
       <c r="C303" s="1">
         <v>14.75</v>
@@ -9283,21 +9823,21 @@
         <v>0.55</v>
       </c>
       <c r="F303" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G303" s="1">
         <v>14.2</v>
       </c>
       <c r="H303" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>300</v>
+        <v>465</v>
       </c>
       <c r="B304" t="s">
-        <v>300</v>
+        <v>465</v>
       </c>
       <c r="C304" s="1">
         <v>13.5</v>
@@ -9309,21 +9849,21 @@
         <v>0.54</v>
       </c>
       <c r="F304" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G304" s="1">
         <v>12.96</v>
       </c>
       <c r="H304" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>301</v>
+        <v>466</v>
       </c>
       <c r="B305" t="s">
-        <v>301</v>
+        <v>467</v>
       </c>
       <c r="C305" s="1">
         <v>9.98</v>
@@ -9335,21 +9875,21 @@
         <v>0.5</v>
       </c>
       <c r="F305" t="s">
-        <v>302</v>
+        <v>468</v>
       </c>
       <c r="G305" s="1">
         <v>9.48</v>
       </c>
       <c r="H305" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>303</v>
+        <v>469</v>
       </c>
       <c r="B306" t="s">
-        <v>303</v>
+        <v>470</v>
       </c>
       <c r="C306" s="1">
         <v>10.49</v>
@@ -9361,21 +9901,21 @@
         <v>0.5</v>
       </c>
       <c r="F306" t="s">
-        <v>155</v>
+        <v>227</v>
       </c>
       <c r="G306" s="1">
         <v>9.99</v>
       </c>
       <c r="H306" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>304</v>
+        <v>471</v>
       </c>
       <c r="B307" t="s">
-        <v>304</v>
+        <v>472</v>
       </c>
       <c r="C307" s="1">
         <v>10.49</v>
@@ -9387,21 +9927,21 @@
         <v>0.5</v>
       </c>
       <c r="F307" t="s">
-        <v>101</v>
+        <v>144</v>
       </c>
       <c r="G307" s="1">
         <v>9.99</v>
       </c>
       <c r="H307" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>305</v>
+        <v>473</v>
       </c>
       <c r="B308" t="s">
-        <v>305</v>
+        <v>474</v>
       </c>
       <c r="C308" s="1">
         <v>10.49</v>
@@ -9413,21 +9953,21 @@
         <v>0.5</v>
       </c>
       <c r="F308" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G308" s="1">
         <v>9.99</v>
       </c>
       <c r="H308" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>306</v>
+        <v>475</v>
       </c>
       <c r="B309" t="s">
-        <v>306</v>
+        <v>475</v>
       </c>
       <c r="C309" s="1">
         <v>10.49</v>
@@ -9439,21 +9979,21 @@
         <v>0.5</v>
       </c>
       <c r="F309" t="s">
-        <v>155</v>
+        <v>227</v>
       </c>
       <c r="G309" s="1">
         <v>9.99</v>
       </c>
       <c r="H309" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>307</v>
+        <v>476</v>
       </c>
       <c r="B310" t="s">
-        <v>307</v>
+        <v>476</v>
       </c>
       <c r="C310" s="1">
         <v>10.45</v>
@@ -9465,21 +10005,21 @@
         <v>0.46</v>
       </c>
       <c r="F310" t="s">
-        <v>101</v>
+        <v>144</v>
       </c>
       <c r="G310" s="1">
         <v>9.99</v>
       </c>
       <c r="H310" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>308</v>
+        <v>477</v>
       </c>
       <c r="B311" t="s">
-        <v>308</v>
+        <v>478</v>
       </c>
       <c r="C311" s="1">
         <v>11.95</v>
@@ -9491,21 +10031,21 @@
         <v>0.45</v>
       </c>
       <c r="F311" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G311" s="1">
         <v>11.5</v>
       </c>
       <c r="H311" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>309</v>
+        <v>479</v>
       </c>
       <c r="B312" t="s">
-        <v>309</v>
+        <v>479</v>
       </c>
       <c r="C312" s="1">
         <v>11.95</v>
@@ -9517,21 +10057,21 @@
         <v>0.45</v>
       </c>
       <c r="F312" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G312" s="1">
         <v>11.5</v>
       </c>
       <c r="H312" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>310</v>
+        <v>480</v>
       </c>
       <c r="B313" t="s">
-        <v>310</v>
+        <v>480</v>
       </c>
       <c r="C313" s="1">
         <v>11.95</v>
@@ -9543,21 +10083,21 @@
         <v>0.45</v>
       </c>
       <c r="F313" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G313" s="1">
         <v>11.5</v>
       </c>
       <c r="H313" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>311</v>
+        <v>481</v>
       </c>
       <c r="B314" t="s">
-        <v>311</v>
+        <v>481</v>
       </c>
       <c r="C314" s="1">
         <v>15.95</v>
@@ -9569,21 +10109,21 @@
         <v>0.39</v>
       </c>
       <c r="F314" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G314" s="1">
         <v>15.56</v>
       </c>
       <c r="H314" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>312</v>
+        <v>482</v>
       </c>
       <c r="B315" t="s">
-        <v>312</v>
+        <v>483</v>
       </c>
       <c r="C315" s="1">
         <v>16.29</v>
@@ -9595,21 +10135,21 @@
         <v>0.34</v>
       </c>
       <c r="F315" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="G315" s="1">
         <v>15.95</v>
       </c>
       <c r="H315" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>313</v>
+        <v>484</v>
       </c>
       <c r="B316" t="s">
-        <v>313</v>
+        <v>485</v>
       </c>
       <c r="C316" s="1">
         <v>14.45</v>
@@ -9621,21 +10161,21 @@
         <v>0.25</v>
       </c>
       <c r="F316" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G316" s="1">
         <v>14.2</v>
       </c>
       <c r="H316" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>314</v>
+        <v>486</v>
       </c>
       <c r="B317" t="s">
-        <v>314</v>
+        <v>487</v>
       </c>
       <c r="C317" s="1">
         <v>11.75</v>
@@ -9647,21 +10187,21 @@
         <v>0.25</v>
       </c>
       <c r="F317" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G317" s="1">
         <v>11.5</v>
       </c>
       <c r="H317" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>315</v>
+        <v>488</v>
       </c>
       <c r="B318" t="s">
-        <v>315</v>
+        <v>488</v>
       </c>
       <c r="C318" s="1">
         <v>11.25</v>
@@ -9673,21 +10213,21 @@
         <v>0.25</v>
       </c>
       <c r="F318" t="s">
-        <v>238</v>
+        <v>365</v>
       </c>
       <c r="G318" s="1">
         <v>11</v>
       </c>
       <c r="H318" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>316</v>
+        <v>489</v>
       </c>
       <c r="B319" t="s">
-        <v>316</v>
+        <v>489</v>
       </c>
       <c r="C319" s="1">
         <v>11.75</v>
@@ -9699,21 +10239,21 @@
         <v>0.25</v>
       </c>
       <c r="F319" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G319" s="1">
         <v>11.5</v>
       </c>
       <c r="H319" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>317</v>
+        <v>490</v>
       </c>
       <c r="B320" t="s">
-        <v>317</v>
+        <v>490</v>
       </c>
       <c r="C320" s="1">
         <v>11.75</v>
@@ -9725,21 +10265,21 @@
         <v>0.25</v>
       </c>
       <c r="F320" t="s">
-        <v>238</v>
+        <v>365</v>
       </c>
       <c r="G320" s="1">
         <v>11.5</v>
       </c>
       <c r="H320" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>318</v>
+        <v>491</v>
       </c>
       <c r="B321" t="s">
-        <v>318</v>
+        <v>491</v>
       </c>
       <c r="C321" s="1">
         <v>14.25</v>
@@ -9751,21 +10291,21 @@
         <v>0.18</v>
       </c>
       <c r="F321" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G321" s="1">
         <v>14.07</v>
       </c>
       <c r="H321" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>319</v>
+        <v>492</v>
       </c>
       <c r="B322" t="s">
-        <v>319</v>
+        <v>493</v>
       </c>
       <c r="C322" s="1">
         <v>14.95</v>
@@ -9777,21 +10317,21 @@
         <v>0.17</v>
       </c>
       <c r="F322" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G322" s="1">
         <v>14.78</v>
       </c>
       <c r="H322" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>320</v>
+        <v>494</v>
       </c>
       <c r="B323" t="s">
-        <v>320</v>
+        <v>495</v>
       </c>
       <c r="C323" s="1">
         <v>14.95</v>
@@ -9803,21 +10343,21 @@
         <v>0.17</v>
       </c>
       <c r="F323" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G323" s="1">
         <v>14.78</v>
       </c>
       <c r="H323" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>321</v>
+        <v>496</v>
       </c>
       <c r="B324" t="s">
-        <v>321</v>
+        <v>497</v>
       </c>
       <c r="C324" s="1">
         <v>14.95</v>
@@ -9829,21 +10369,21 @@
         <v>0.17</v>
       </c>
       <c r="F324" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G324" s="1">
         <v>14.78</v>
       </c>
       <c r="H324" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>322</v>
+        <v>498</v>
       </c>
       <c r="B325" t="s">
-        <v>322</v>
+        <v>498</v>
       </c>
       <c r="C325" s="1">
         <v>14.95</v>
@@ -9855,21 +10395,21 @@
         <v>0.17</v>
       </c>
       <c r="F325" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G325" s="1">
         <v>14.78</v>
       </c>
       <c r="H325" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>323</v>
+        <v>499</v>
       </c>
       <c r="B326" t="s">
-        <v>323</v>
+        <v>499</v>
       </c>
       <c r="C326" s="1">
         <v>14.95</v>
@@ -9881,21 +10421,21 @@
         <v>0.17</v>
       </c>
       <c r="F326" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G326" s="1">
         <v>14.78</v>
       </c>
       <c r="H326" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>324</v>
+        <v>500</v>
       </c>
       <c r="B327" t="s">
-        <v>324</v>
+        <v>501</v>
       </c>
       <c r="C327" s="1">
         <v>10.45</v>
@@ -9907,21 +10447,21 @@
         <v>0.11</v>
       </c>
       <c r="F327" t="s">
-        <v>325</v>
+        <v>502</v>
       </c>
       <c r="G327" s="1">
         <v>10.34</v>
       </c>
       <c r="H327" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>326</v>
+        <v>503</v>
       </c>
       <c r="B328" t="s">
-        <v>326</v>
+        <v>504</v>
       </c>
       <c r="C328" s="1">
         <v>10.45</v>
@@ -9933,21 +10473,21 @@
         <v>0.11</v>
       </c>
       <c r="F328" t="s">
-        <v>325</v>
+        <v>502</v>
       </c>
       <c r="G328" s="1">
         <v>10.34</v>
       </c>
       <c r="H328" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>327</v>
+        <v>505</v>
       </c>
       <c r="B329" t="s">
-        <v>327</v>
+        <v>505</v>
       </c>
       <c r="C329" s="1">
         <v>10.45</v>
@@ -9959,21 +10499,21 @@
         <v>0.11</v>
       </c>
       <c r="F329" t="s">
-        <v>325</v>
+        <v>502</v>
       </c>
       <c r="G329" s="1">
         <v>10.34</v>
       </c>
       <c r="H329" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>328</v>
+        <v>506</v>
       </c>
       <c r="B330" t="s">
-        <v>328</v>
+        <v>507</v>
       </c>
       <c r="C330" s="1">
         <v>12.24</v>
@@ -9985,21 +10525,21 @@
         <v>0.05</v>
       </c>
       <c r="F330" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="G330" s="1">
         <v>12.19</v>
       </c>
       <c r="H330" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>329</v>
+        <v>508</v>
       </c>
       <c r="B331" t="s">
-        <v>329</v>
+        <v>508</v>
       </c>
       <c r="C331" s="1">
         <v>12.24</v>
@@ -10011,21 +10551,21 @@
         <v>0.05</v>
       </c>
       <c r="F331" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="G331" s="1">
         <v>12.19</v>
       </c>
       <c r="H331" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>330</v>
+        <v>509</v>
       </c>
       <c r="B332" t="s">
-        <v>330</v>
+        <v>509</v>
       </c>
       <c r="C332" s="1">
         <v>14.25</v>
@@ -10037,21 +10577,21 @@
         <v>0.05</v>
       </c>
       <c r="F332" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G332" s="1">
         <v>14.2</v>
       </c>
       <c r="H332" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>331</v>
+        <v>510</v>
       </c>
       <c r="B333" t="s">
-        <v>331</v>
+        <v>510</v>
       </c>
       <c r="C333" s="1">
         <v>14.25</v>
@@ -10063,21 +10603,21 @@
         <v>0.05</v>
       </c>
       <c r="F333" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="G333" s="1">
         <v>14.2</v>
       </c>
       <c r="H333" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>332</v>
+        <v>511</v>
       </c>
       <c r="B334" t="s">
-        <v>332</v>
+        <v>512</v>
       </c>
       <c r="C334" s="1">
         <v>9.99</v>
@@ -10089,13 +10629,13 @@
         <v>0.04</v>
       </c>
       <c r="F334" t="s">
-        <v>188</v>
+        <v>282</v>
       </c>
       <c r="G334" s="1">
         <v>9.95</v>
       </c>
       <c r="H334" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
